--- a/data/simuladores/simulador-tarifarios-gas/tarifarios_gas_natural_Tiago_Felicia.xlsx
+++ b/data/simuladores/simulador-tarifarios-gas/tarifarios_gas_natural_Tiago_Felicia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tiago\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E0B4611-9551-4B30-A467-4D26C3AB7407}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81E28E8D-4666-4612-884C-E97B81F274CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3029,10 +3029,10 @@
         <v>18</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="G30" s="5" t="s">
         <v>25</v>
@@ -3075,10 +3075,10 @@
         <v>18</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="G31" s="5" t="s">
         <v>25</v>
@@ -3121,10 +3121,10 @@
         <v>18</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="G32" s="5" t="s">
         <v>25</v>
@@ -3167,10 +3167,10 @@
         <v>18</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="G33" s="5" t="s">
         <v>25</v>

--- a/data/simuladores/simulador-tarifarios-gas/tarifarios_gas_natural_Tiago_Felicia.xlsx
+++ b/data/simuladores/simulador-tarifarios-gas/tarifarios_gas_natural_Tiago_Felicia.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tiago\Downloads\Claude Code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC2F2B14-AE11-43B0-85EA-60FFD3B61FC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BFA8EAF-3213-4397-9D43-FBE1879A33A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tarifas_Gas_Master" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="Constantes" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Tarifas_Gas_Master!$A$1:$AB$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Tarifas_Gas_Master!$A$1:$AB$193</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2581" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2581" uniqueCount="366">
   <si>
     <t>Comercializador</t>
   </si>
@@ -1072,9 +1072,6 @@
   </si>
   <si>
     <t>Há a possibilidade de ter 1,23 € de desconto extra por cada Amigo angariado.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Oferta de 3 € + IVA (3,69 €/mês) nos primeiros 10 meses de contrato. Há a possibilidade de ter 1,23 € de desconto extra por cada Amigo angariado.</t>
   </si>
   <si>
     <t>Há oferta da 12ª mensalidade (não refletida nos valores). Há a possibilidade de ter 1,23 € de desconto extra por cada Amigo angariado.</t>
@@ -1192,7 +1189,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1208,12 +1205,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1245,7 +1236,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1263,14 +1254,6 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1728,7 +1711,7 @@
         <v>15</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>16</v>
@@ -1771,7 +1754,7 @@
         <v>15</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>16</v>
@@ -1814,7 +1797,7 @@
         <v>15</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>16</v>
@@ -1857,7 +1840,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>16</v>
@@ -2416,7 +2399,7 @@
         <v>24</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>16</v>
@@ -2459,7 +2442,7 @@
         <v>24</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>16</v>
@@ -2502,7 +2485,7 @@
         <v>24</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>16</v>
@@ -2545,7 +2528,7 @@
         <v>24</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>16</v>
@@ -2760,7 +2743,7 @@
         <v>32</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>16</v>
@@ -2803,7 +2786,7 @@
         <v>32</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>16</v>
@@ -2846,7 +2829,7 @@
         <v>32</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>16</v>
@@ -2889,7 +2872,7 @@
         <v>32</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C29" s="5" t="s">
         <v>16</v>
@@ -2932,7 +2915,7 @@
         <v>32</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>16</v>
@@ -2975,7 +2958,7 @@
         <v>32</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>16</v>
@@ -3018,7 +3001,7 @@
         <v>32</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>16</v>
@@ -3061,7 +3044,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>16</v>
@@ -3113,10 +3096,10 @@
         <v>17</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G34" s="5">
         <v>1</v>
@@ -3156,10 +3139,10 @@
         <v>17</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G35" s="5">
         <v>2</v>
@@ -3199,10 +3182,10 @@
         <v>17</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G36" s="5">
         <v>3</v>
@@ -3242,10 +3225,10 @@
         <v>17</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G37" s="5">
         <v>4</v>
@@ -3615,2671 +3598,2599 @@
       <c r="AA45" s="4"/>
       <c r="AB45" s="4"/>
     </row>
-    <row r="46" spans="1:28" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="11" t="s">
+    <row r="46" spans="1:28" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B46" s="11" t="s">
+      <c r="B46" s="5" t="s">
         <v>315</v>
       </c>
-      <c r="C46" s="11" t="s">
+      <c r="C46" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D46" s="11" t="s">
+      <c r="D46" s="5" t="s">
         <v>299</v>
       </c>
-      <c r="E46" s="11" t="s">
+      <c r="E46" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F46" s="11" t="s">
+      <c r="F46" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G46" s="11">
+      <c r="G46" s="5">
         <v>1</v>
       </c>
-      <c r="H46" s="11">
+      <c r="H46" s="5">
         <v>0.14419999999999999</v>
       </c>
-      <c r="I46" s="11">
+      <c r="I46" s="5">
         <v>8.4075999999999998E-2</v>
       </c>
-      <c r="J46" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="K46" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="P46" s="11">
+      <c r="J46" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K46" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="P46" s="5">
         <v>1.23</v>
       </c>
-      <c r="R46" s="11" t="s">
+      <c r="R46" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="T46" s="11" t="s">
+      <c r="T46" s="5" t="s">
         <v>312</v>
       </c>
-      <c r="X46" s="12"/>
-      <c r="Y46" s="12"/>
-      <c r="Z46" s="12"/>
-      <c r="AA46" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="AB46" s="12"/>
-    </row>
-    <row r="47" spans="1:28" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="11" t="s">
+      <c r="X46" s="4"/>
+      <c r="Y46" s="4"/>
+      <c r="Z46" s="4"/>
+      <c r="AA46" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="AB46" s="4"/>
+    </row>
+    <row r="47" spans="1:28" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B47" s="11" t="s">
+      <c r="B47" s="5" t="s">
         <v>315</v>
       </c>
-      <c r="C47" s="11" t="s">
+      <c r="C47" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D47" s="11" t="s">
+      <c r="D47" s="5" t="s">
         <v>299</v>
       </c>
-      <c r="E47" s="11" t="s">
+      <c r="E47" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F47" s="11" t="s">
+      <c r="F47" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G47" s="11">
+      <c r="G47" s="5">
         <v>2</v>
       </c>
-      <c r="H47" s="11">
+      <c r="H47" s="5">
         <v>0.23899999999999999</v>
       </c>
-      <c r="I47" s="11">
+      <c r="I47" s="5">
         <v>8.3886000000000002E-2</v>
       </c>
-      <c r="J47" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="K47" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="P47" s="11">
+      <c r="J47" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K47" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="P47" s="5">
         <v>1.23</v>
       </c>
-      <c r="R47" s="11" t="s">
+      <c r="R47" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="T47" s="11" t="s">
+      <c r="T47" s="5" t="s">
         <v>312</v>
       </c>
-      <c r="X47" s="12"/>
-      <c r="Y47" s="12"/>
-      <c r="Z47" s="12"/>
-      <c r="AA47" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="AB47" s="12"/>
-    </row>
-    <row r="48" spans="1:28" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="11" t="s">
+      <c r="X47" s="4"/>
+      <c r="Y47" s="4"/>
+      <c r="Z47" s="4"/>
+      <c r="AA47" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="AB47" s="4"/>
+    </row>
+    <row r="48" spans="1:28" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B48" s="11" t="s">
+      <c r="B48" s="5" t="s">
         <v>315</v>
       </c>
-      <c r="C48" s="11" t="s">
+      <c r="C48" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D48" s="11" t="s">
+      <c r="D48" s="5" t="s">
         <v>299</v>
       </c>
-      <c r="E48" s="11" t="s">
+      <c r="E48" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F48" s="11" t="s">
+      <c r="F48" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G48" s="11">
+      <c r="G48" s="5">
         <v>3</v>
       </c>
-      <c r="H48" s="11">
+      <c r="H48" s="5">
         <v>0.37330000000000002</v>
       </c>
-      <c r="I48" s="11">
+      <c r="I48" s="5">
         <v>8.1201999999999996E-2</v>
       </c>
-      <c r="J48" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="K48" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="P48" s="11">
+      <c r="J48" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K48" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="P48" s="5">
         <v>1.23</v>
       </c>
-      <c r="R48" s="11" t="s">
+      <c r="R48" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="T48" s="11" t="s">
+      <c r="T48" s="5" t="s">
         <v>312</v>
       </c>
-      <c r="X48" s="12"/>
-      <c r="Y48" s="12"/>
-      <c r="Z48" s="12"/>
-      <c r="AA48" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="AB48" s="12"/>
-    </row>
-    <row r="49" spans="1:28" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="11" t="s">
+      <c r="X48" s="4"/>
+      <c r="Y48" s="4"/>
+      <c r="Z48" s="4"/>
+      <c r="AA48" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="AB48" s="4"/>
+    </row>
+    <row r="49" spans="1:28" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B49" s="11" t="s">
+      <c r="B49" s="5" t="s">
         <v>315</v>
       </c>
-      <c r="C49" s="11" t="s">
+      <c r="C49" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D49" s="11" t="s">
+      <c r="D49" s="5" t="s">
         <v>299</v>
       </c>
-      <c r="E49" s="11" t="s">
+      <c r="E49" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F49" s="11" t="s">
+      <c r="F49" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G49" s="11">
+      <c r="G49" s="5">
         <v>4</v>
       </c>
-      <c r="H49" s="11">
+      <c r="H49" s="5">
         <v>0.69</v>
       </c>
-      <c r="I49" s="11">
+      <c r="I49" s="5">
         <v>8.0393000000000006E-2</v>
       </c>
-      <c r="J49" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="K49" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="P49" s="11">
+      <c r="J49" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K49" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="P49" s="5">
         <v>1.23</v>
       </c>
-      <c r="R49" s="11" t="s">
+      <c r="R49" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="T49" s="11" t="s">
+      <c r="T49" s="5" t="s">
         <v>312</v>
       </c>
-      <c r="X49" s="12"/>
-      <c r="Y49" s="12"/>
-      <c r="Z49" s="12"/>
-      <c r="AA49" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="AB49" s="12"/>
-    </row>
-    <row r="50" spans="1:28" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="11" t="s">
+      <c r="X49" s="4"/>
+      <c r="Y49" s="4"/>
+      <c r="Z49" s="4"/>
+      <c r="AA49" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="AB49" s="4"/>
+    </row>
+    <row r="50" spans="1:28" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B50" s="11" t="s">
+      <c r="B50" s="5" t="s">
         <v>331</v>
       </c>
-      <c r="C50" s="11" t="s">
+      <c r="C50" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D50" s="11" t="s">
+      <c r="D50" s="5" t="s">
         <v>299</v>
       </c>
-      <c r="E50" s="11" t="s">
+      <c r="E50" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F50" s="11" t="s">
+      <c r="F50" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G50" s="11">
+      <c r="G50" s="5">
         <v>1</v>
       </c>
-      <c r="H50" s="11">
+      <c r="H50" s="5">
         <v>0.18001200000000001</v>
       </c>
-      <c r="I50" s="11">
+      <c r="I50" s="5">
         <v>0.112673</v>
       </c>
-      <c r="J50" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="K50" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="L50" s="11">
+      <c r="J50" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K50" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="L50" s="5">
         <v>3.69</v>
       </c>
-      <c r="N50" s="11">
+      <c r="N50" s="5">
         <v>10</v>
       </c>
-      <c r="P50" s="11">
+      <c r="P50" s="5">
         <v>1.23</v>
       </c>
-      <c r="R50" s="11" t="s">
+      <c r="R50" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="T50" s="11" t="s">
+      <c r="T50" s="5" t="s">
         <v>332</v>
       </c>
-      <c r="X50" s="12"/>
-      <c r="Y50" s="12"/>
-      <c r="Z50" s="12"/>
-      <c r="AA50" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="AB50" s="12"/>
-    </row>
-    <row r="51" spans="1:28" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="11" t="s">
+      <c r="X50" s="4"/>
+      <c r="Y50" s="4"/>
+      <c r="Z50" s="4"/>
+      <c r="AA50" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="AB50" s="4"/>
+    </row>
+    <row r="51" spans="1:28" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B51" s="11" t="s">
+      <c r="B51" s="5" t="s">
         <v>331</v>
       </c>
-      <c r="C51" s="11" t="s">
+      <c r="C51" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D51" s="11" t="s">
+      <c r="D51" s="5" t="s">
         <v>299</v>
       </c>
-      <c r="E51" s="11" t="s">
+      <c r="E51" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F51" s="11" t="s">
+      <c r="F51" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G51" s="11">
+      <c r="G51" s="5">
         <v>2</v>
       </c>
-      <c r="H51" s="11">
+      <c r="H51" s="5">
         <v>0.25552799999999998</v>
       </c>
-      <c r="I51" s="11">
+      <c r="I51" s="5">
         <v>0.108971</v>
       </c>
-      <c r="J51" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="K51" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="L51" s="11">
+      <c r="J51" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K51" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="L51" s="5">
         <v>3.69</v>
       </c>
-      <c r="N51" s="11">
+      <c r="N51" s="5">
         <v>10</v>
       </c>
-      <c r="P51" s="11">
+      <c r="P51" s="5">
         <v>1.23</v>
       </c>
-      <c r="R51" s="11" t="s">
+      <c r="R51" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="T51" s="11" t="s">
+      <c r="T51" s="5" t="s">
         <v>332</v>
       </c>
-      <c r="X51" s="12"/>
-      <c r="Y51" s="12"/>
-      <c r="Z51" s="12"/>
-      <c r="AA51" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="AB51" s="12"/>
-    </row>
-    <row r="52" spans="1:28" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="11" t="s">
+      <c r="X51" s="4"/>
+      <c r="Y51" s="4"/>
+      <c r="Z51" s="4"/>
+      <c r="AA51" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="AB51" s="4"/>
+    </row>
+    <row r="52" spans="1:28" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B52" s="11" t="s">
+      <c r="B52" s="5" t="s">
         <v>331</v>
       </c>
-      <c r="C52" s="11" t="s">
+      <c r="C52" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D52" s="11" t="s">
+      <c r="D52" s="5" t="s">
         <v>299</v>
       </c>
-      <c r="E52" s="11" t="s">
+      <c r="E52" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F52" s="11" t="s">
+      <c r="F52" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G52" s="11">
+      <c r="G52" s="5">
         <v>3</v>
       </c>
-      <c r="H52" s="11">
+      <c r="H52" s="5">
         <v>0.41445599999999999</v>
       </c>
-      <c r="I52" s="11">
+      <c r="I52" s="5">
         <v>0.10127</v>
       </c>
-      <c r="J52" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="K52" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="L52" s="11">
+      <c r="J52" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K52" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="L52" s="5">
         <v>3.69</v>
       </c>
-      <c r="N52" s="11">
+      <c r="N52" s="5">
         <v>10</v>
       </c>
-      <c r="P52" s="11">
+      <c r="P52" s="5">
         <v>1.23</v>
       </c>
-      <c r="R52" s="11" t="s">
+      <c r="R52" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="T52" s="11" t="s">
+      <c r="T52" s="5" t="s">
         <v>332</v>
       </c>
-      <c r="X52" s="12"/>
-      <c r="Y52" s="12"/>
-      <c r="Z52" s="12"/>
-      <c r="AA52" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="AB52" s="12"/>
-    </row>
-    <row r="53" spans="1:28" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="11" t="s">
+      <c r="X52" s="4"/>
+      <c r="Y52" s="4"/>
+      <c r="Z52" s="4"/>
+      <c r="AA52" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="AB52" s="4"/>
+    </row>
+    <row r="53" spans="1:28" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B53" s="11" t="s">
+      <c r="B53" s="5" t="s">
         <v>331</v>
       </c>
-      <c r="C53" s="11" t="s">
+      <c r="C53" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D53" s="11" t="s">
+      <c r="D53" s="5" t="s">
         <v>299</v>
       </c>
-      <c r="E53" s="11" t="s">
+      <c r="E53" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F53" s="11" t="s">
+      <c r="F53" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G53" s="11">
+      <c r="G53" s="5">
         <v>4</v>
       </c>
-      <c r="H53" s="11">
+      <c r="H53" s="5">
         <v>0.67325999999999997</v>
       </c>
-      <c r="I53" s="11">
+      <c r="I53" s="5">
         <v>0.10046099999999999</v>
       </c>
-      <c r="J53" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="K53" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="L53" s="11">
+      <c r="J53" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K53" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="L53" s="5">
         <v>3.69</v>
       </c>
-      <c r="N53" s="11">
+      <c r="N53" s="5">
         <v>10</v>
       </c>
-      <c r="P53" s="11">
+      <c r="P53" s="5">
         <v>1.23</v>
       </c>
-      <c r="R53" s="11" t="s">
+      <c r="R53" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="T53" s="11" t="s">
+      <c r="T53" s="5" t="s">
         <v>332</v>
       </c>
-      <c r="X53" s="12"/>
-      <c r="Y53" s="12"/>
-      <c r="Z53" s="12"/>
-      <c r="AA53" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="AB53" s="12"/>
-    </row>
-    <row r="54" spans="1:28" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="11" t="s">
+      <c r="X53" s="4"/>
+      <c r="Y53" s="4"/>
+      <c r="Z53" s="4"/>
+      <c r="AA53" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="AB53" s="4"/>
+    </row>
+    <row r="54" spans="1:28" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B54" s="11" t="s">
+      <c r="B54" s="5" t="s">
         <v>330</v>
       </c>
-      <c r="C54" s="11" t="s">
+      <c r="C54" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D54" s="11" t="s">
+      <c r="D54" s="5" t="s">
         <v>299</v>
       </c>
-      <c r="E54" s="11" t="s">
+      <c r="E54" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="F54" s="11" t="s">
+      <c r="F54" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="G54" s="11">
+      <c r="G54" s="5">
         <v>1</v>
       </c>
-      <c r="H54" s="11">
+      <c r="H54" s="5">
         <v>0.18215500000000001</v>
       </c>
-      <c r="I54" s="11">
+      <c r="I54" s="5">
         <v>0.114014</v>
       </c>
-      <c r="J54" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="K54" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="L54" s="11">
+      <c r="J54" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K54" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="L54" s="5">
         <v>3.69</v>
       </c>
-      <c r="N54" s="11">
+      <c r="N54" s="5">
         <v>10</v>
       </c>
-      <c r="P54" s="11">
+      <c r="P54" s="5">
         <v>1.23</v>
       </c>
-      <c r="R54" s="11" t="s">
+      <c r="R54" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="T54" s="11" t="s">
+      <c r="T54" s="5" t="s">
         <v>332</v>
       </c>
-      <c r="X54" s="12"/>
-      <c r="Y54" s="12"/>
-      <c r="Z54" s="12"/>
-      <c r="AA54" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="AB54" s="12"/>
-    </row>
-    <row r="55" spans="1:28" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="11" t="s">
+      <c r="X54" s="4"/>
+      <c r="Y54" s="4"/>
+      <c r="Z54" s="4"/>
+      <c r="AA54" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="AB54" s="4"/>
+    </row>
+    <row r="55" spans="1:28" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B55" s="11" t="s">
+      <c r="B55" s="5" t="s">
         <v>330</v>
       </c>
-      <c r="C55" s="11" t="s">
+      <c r="C55" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D55" s="11" t="s">
+      <c r="D55" s="5" t="s">
         <v>299</v>
       </c>
-      <c r="E55" s="11" t="s">
+      <c r="E55" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="F55" s="11" t="s">
+      <c r="F55" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="G55" s="11">
+      <c r="G55" s="5">
         <v>2</v>
       </c>
-      <c r="H55" s="11">
+      <c r="H55" s="5">
         <v>0.25857000000000002</v>
       </c>
-      <c r="I55" s="11">
+      <c r="I55" s="5">
         <v>0.110268</v>
       </c>
-      <c r="J55" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="K55" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="L55" s="11">
+      <c r="J55" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K55" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="L55" s="5">
         <v>3.69</v>
       </c>
-      <c r="N55" s="11">
+      <c r="N55" s="5">
         <v>10</v>
       </c>
-      <c r="P55" s="11">
+      <c r="P55" s="5">
         <v>1.23</v>
       </c>
-      <c r="R55" s="11" t="s">
+      <c r="R55" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="T55" s="11" t="s">
+      <c r="T55" s="5" t="s">
         <v>332</v>
       </c>
-      <c r="X55" s="12"/>
-      <c r="Y55" s="12"/>
-      <c r="Z55" s="12"/>
-      <c r="AA55" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="AB55" s="12"/>
-    </row>
-    <row r="56" spans="1:28" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="11" t="s">
+      <c r="X55" s="4"/>
+      <c r="Y55" s="4"/>
+      <c r="Z55" s="4"/>
+      <c r="AA55" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="AB55" s="4"/>
+    </row>
+    <row r="56" spans="1:28" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B56" s="11" t="s">
+      <c r="B56" s="5" t="s">
         <v>330</v>
       </c>
-      <c r="C56" s="11" t="s">
+      <c r="C56" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D56" s="11" t="s">
+      <c r="D56" s="5" t="s">
         <v>299</v>
       </c>
-      <c r="E56" s="11" t="s">
+      <c r="E56" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="F56" s="11" t="s">
+      <c r="F56" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="G56" s="11">
+      <c r="G56" s="5">
         <v>3</v>
       </c>
-      <c r="H56" s="11">
+      <c r="H56" s="5">
         <v>0.41938999999999999</v>
       </c>
-      <c r="I56" s="11">
+      <c r="I56" s="5">
         <v>0.102476</v>
       </c>
-      <c r="J56" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="K56" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="L56" s="11">
+      <c r="J56" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K56" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="L56" s="5">
         <v>3.69</v>
       </c>
-      <c r="N56" s="11">
+      <c r="N56" s="5">
         <v>10</v>
       </c>
-      <c r="P56" s="11">
+      <c r="P56" s="5">
         <v>1.23</v>
       </c>
-      <c r="R56" s="11" t="s">
+      <c r="R56" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="T56" s="11" t="s">
+      <c r="T56" s="5" t="s">
         <v>332</v>
       </c>
-      <c r="X56" s="12"/>
-      <c r="Y56" s="12"/>
-      <c r="Z56" s="12"/>
-      <c r="AA56" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="AB56" s="12"/>
-    </row>
-    <row r="57" spans="1:28" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="11" t="s">
+      <c r="X56" s="4"/>
+      <c r="Y56" s="4"/>
+      <c r="Z56" s="4"/>
+      <c r="AA56" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="AB56" s="4"/>
+    </row>
+    <row r="57" spans="1:28" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B57" s="11" t="s">
+      <c r="B57" s="5" t="s">
         <v>330</v>
       </c>
-      <c r="C57" s="11" t="s">
+      <c r="C57" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D57" s="11" t="s">
+      <c r="D57" s="5" t="s">
         <v>299</v>
       </c>
-      <c r="E57" s="11" t="s">
+      <c r="E57" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="F57" s="11" t="s">
+      <c r="F57" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="G57" s="11">
+      <c r="G57" s="5">
         <v>4</v>
       </c>
-      <c r="H57" s="11">
+      <c r="H57" s="5">
         <v>0.68127499999999996</v>
       </c>
-      <c r="I57" s="11">
+      <c r="I57" s="5">
         <v>0.101657</v>
       </c>
-      <c r="J57" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="K57" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="L57" s="11">
+      <c r="J57" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K57" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="L57" s="5">
         <v>3.69</v>
       </c>
-      <c r="N57" s="11">
+      <c r="N57" s="5">
         <v>10</v>
       </c>
-      <c r="P57" s="11">
+      <c r="P57" s="5">
         <v>1.23</v>
       </c>
-      <c r="R57" s="11" t="s">
+      <c r="R57" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="T57" s="11" t="s">
+      <c r="T57" s="5" t="s">
         <v>332</v>
       </c>
-      <c r="X57" s="12"/>
-      <c r="Y57" s="12"/>
-      <c r="Z57" s="12"/>
-      <c r="AA57" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="AB57" s="12"/>
-    </row>
-    <row r="58" spans="1:28" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="11" t="s">
+      <c r="X57" s="4"/>
+      <c r="Y57" s="4"/>
+      <c r="Z57" s="4"/>
+      <c r="AA57" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="AB57" s="4"/>
+    </row>
+    <row r="58" spans="1:28" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B58" s="11" t="s">
+      <c r="B58" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D58" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="E58" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="F58" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="G58" s="5">
+        <v>1</v>
+      </c>
+      <c r="H58" s="5">
+        <v>0.18429799999999999</v>
+      </c>
+      <c r="I58" s="5">
+        <v>0.115355</v>
+      </c>
+      <c r="J58" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K58" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="L58" s="5">
+        <v>3.69</v>
+      </c>
+      <c r="N58" s="5">
+        <v>10</v>
+      </c>
+      <c r="P58" s="5">
+        <v>1.23</v>
+      </c>
+      <c r="R58" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="T58" s="5" t="s">
+        <v>332</v>
+      </c>
+      <c r="X58" s="4"/>
+      <c r="Y58" s="4"/>
+      <c r="Z58" s="4"/>
+      <c r="AA58" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="AB58" s="4"/>
+    </row>
+    <row r="59" spans="1:28" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D59" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="E59" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="F59" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="G59" s="5">
+        <v>2</v>
+      </c>
+      <c r="H59" s="5">
+        <v>0.26161200000000001</v>
+      </c>
+      <c r="I59" s="5">
+        <v>0.111565</v>
+      </c>
+      <c r="J59" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K59" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="L59" s="5">
+        <v>3.69</v>
+      </c>
+      <c r="N59" s="5">
+        <v>10</v>
+      </c>
+      <c r="P59" s="5">
+        <v>1.23</v>
+      </c>
+      <c r="R59" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="T59" s="5" t="s">
+        <v>332</v>
+      </c>
+      <c r="X59" s="4"/>
+      <c r="Y59" s="4"/>
+      <c r="Z59" s="4"/>
+      <c r="AA59" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="AB59" s="4"/>
+    </row>
+    <row r="60" spans="1:28" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D60" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="E60" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="F60" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="G60" s="5">
+        <v>3</v>
+      </c>
+      <c r="H60" s="5">
+        <v>0.42432399999999998</v>
+      </c>
+      <c r="I60" s="5">
+        <v>0.103682</v>
+      </c>
+      <c r="J60" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K60" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="L60" s="5">
+        <v>3.69</v>
+      </c>
+      <c r="N60" s="5">
+        <v>10</v>
+      </c>
+      <c r="P60" s="5">
+        <v>1.23</v>
+      </c>
+      <c r="R60" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="T60" s="5" t="s">
+        <v>332</v>
+      </c>
+      <c r="X60" s="4"/>
+      <c r="Y60" s="4"/>
+      <c r="Z60" s="4"/>
+      <c r="AA60" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="AB60" s="4"/>
+    </row>
+    <row r="61" spans="1:28" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D61" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="E61" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="F61" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="G61" s="5">
+        <v>4</v>
+      </c>
+      <c r="H61" s="5">
+        <v>0.68928999999999996</v>
+      </c>
+      <c r="I61" s="5">
+        <v>0.102853</v>
+      </c>
+      <c r="J61" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K61" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="L61" s="5">
+        <v>3.69</v>
+      </c>
+      <c r="N61" s="5">
+        <v>10</v>
+      </c>
+      <c r="P61" s="5">
+        <v>1.23</v>
+      </c>
+      <c r="R61" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="T61" s="5" t="s">
+        <v>332</v>
+      </c>
+      <c r="X61" s="4"/>
+      <c r="Y61" s="4"/>
+      <c r="Z61" s="4"/>
+      <c r="AA61" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="AB61" s="4"/>
+    </row>
+    <row r="62" spans="1:28" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="C62" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D62" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="E62" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F62" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G62" s="5">
+        <v>1</v>
+      </c>
+      <c r="H62" s="5">
+        <v>0.1288</v>
+      </c>
+      <c r="I62" s="5">
+        <v>8.5581000000000004E-2</v>
+      </c>
+      <c r="J62" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K62" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="P62" s="5">
+        <v>1.23</v>
+      </c>
+      <c r="R62" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="T62" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="X62" s="4"/>
+      <c r="Y62" s="4"/>
+      <c r="Z62" s="4"/>
+      <c r="AA62" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="AB62" s="4"/>
+    </row>
+    <row r="63" spans="1:28" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="C63" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D63" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="E63" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F63" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G63" s="5">
+        <v>2</v>
+      </c>
+      <c r="H63" s="5">
+        <v>0.23899999999999999</v>
+      </c>
+      <c r="I63" s="5">
+        <v>8.1878999999999993E-2</v>
+      </c>
+      <c r="J63" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K63" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="P63" s="5">
+        <v>1.23</v>
+      </c>
+      <c r="R63" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="T63" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="X63" s="4"/>
+      <c r="Y63" s="4"/>
+      <c r="Z63" s="4"/>
+      <c r="AA63" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="AB63" s="4"/>
+    </row>
+    <row r="64" spans="1:28" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="C64" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D64" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="E64" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F64" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G64" s="5">
+        <v>1</v>
+      </c>
+      <c r="H64" s="5">
+        <v>0.15165300000000001</v>
+      </c>
+      <c r="I64" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="J64" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K64" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="P64" s="5">
+        <v>1.23</v>
+      </c>
+      <c r="R64" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="T64" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="X64" s="4"/>
+      <c r="Y64" s="4"/>
+      <c r="Z64" s="4"/>
+      <c r="AA64" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="AB64" s="4"/>
+    </row>
+    <row r="65" spans="1:28" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="C65" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D65" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="E65" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F65" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G65" s="5">
+        <v>2</v>
+      </c>
+      <c r="H65" s="5">
+        <v>0.187253</v>
+      </c>
+      <c r="I65" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="J65" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K65" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="P65" s="5">
+        <v>1.23</v>
+      </c>
+      <c r="R65" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="T65" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="X65" s="4"/>
+      <c r="Y65" s="4"/>
+      <c r="Z65" s="4"/>
+      <c r="AA65" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="AB65" s="4"/>
+    </row>
+    <row r="66" spans="1:28" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="C66" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D66" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="E66" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F66" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G66" s="5">
+        <v>3</v>
+      </c>
+      <c r="H66" s="5">
+        <v>0.22175300000000001</v>
+      </c>
+      <c r="I66" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="J66" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K66" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="P66" s="5">
+        <v>1.23</v>
+      </c>
+      <c r="R66" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="T66" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="X66" s="4"/>
+      <c r="Y66" s="4"/>
+      <c r="Z66" s="4"/>
+      <c r="AA66" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="AB66" s="4"/>
+    </row>
+    <row r="67" spans="1:28" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="C67" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D67" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="E67" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F67" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G67" s="5">
+        <v>4</v>
+      </c>
+      <c r="H67" s="5">
+        <v>0.28145300000000001</v>
+      </c>
+      <c r="I67" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="J67" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K67" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="P67" s="5">
+        <v>1.23</v>
+      </c>
+      <c r="R67" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="T67" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="X67" s="4"/>
+      <c r="Y67" s="4"/>
+      <c r="Z67" s="4"/>
+      <c r="AA67" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="AB67" s="4"/>
+    </row>
+    <row r="68" spans="1:28" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="C68" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D68" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="E68" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F68" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G68" s="5">
+        <v>1</v>
+      </c>
+      <c r="H68" s="5">
+        <v>0.1646</v>
+      </c>
+      <c r="I68" s="5">
+        <v>9.9929000000000004E-2</v>
+      </c>
+      <c r="J68" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K68" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="P68" s="5">
+        <v>1.23</v>
+      </c>
+      <c r="R68" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="T68" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="X68" s="4"/>
+      <c r="Y68" s="4"/>
+      <c r="Z68" s="4"/>
+      <c r="AA68" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="AB68" s="4"/>
+    </row>
+    <row r="69" spans="1:28" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="C69" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D69" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="E69" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F69" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G69" s="5">
+        <v>2</v>
+      </c>
+      <c r="H69" s="5">
+        <v>0.28120000000000001</v>
+      </c>
+      <c r="I69" s="5">
+        <v>9.9173999999999998E-2</v>
+      </c>
+      <c r="J69" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K69" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="P69" s="5">
+        <v>1.23</v>
+      </c>
+      <c r="R69" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="T69" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="X69" s="4"/>
+      <c r="Y69" s="4"/>
+      <c r="Z69" s="4"/>
+      <c r="AA69" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="AB69" s="4"/>
+    </row>
+    <row r="70" spans="1:28" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="C70" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D70" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="E70" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F70" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G70" s="5">
+        <v>3</v>
+      </c>
+      <c r="H70" s="5">
+        <v>0.4632</v>
+      </c>
+      <c r="I70" s="5">
+        <v>9.5699000000000006E-2</v>
+      </c>
+      <c r="J70" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K70" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="P70" s="5">
+        <v>1.23</v>
+      </c>
+      <c r="R70" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="T70" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="X70" s="4"/>
+      <c r="Y70" s="4"/>
+      <c r="Z70" s="4"/>
+      <c r="AA70" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="AB70" s="4"/>
+    </row>
+    <row r="71" spans="1:28" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B71" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="C71" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D71" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="E71" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F71" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G71" s="5">
+        <v>4</v>
+      </c>
+      <c r="H71" s="5">
+        <v>0.91469999999999996</v>
+      </c>
+      <c r="I71" s="5">
+        <v>9.4269000000000006E-2</v>
+      </c>
+      <c r="J71" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K71" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="P71" s="5">
+        <v>1.23</v>
+      </c>
+      <c r="R71" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="T71" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="X71" s="4"/>
+      <c r="Y71" s="4"/>
+      <c r="Z71" s="4"/>
+      <c r="AA71" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="AB71" s="4"/>
+    </row>
+    <row r="72" spans="1:28" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="C72" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D72" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="E72" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F72" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G72" s="5">
+        <v>1</v>
+      </c>
+      <c r="H72" s="5">
+        <v>0.14419999999999999</v>
+      </c>
+      <c r="I72" s="5">
+        <v>8.4075999999999998E-2</v>
+      </c>
+      <c r="J72" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K72" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="R72" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="T72" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="X72" s="4"/>
+      <c r="Y72" s="4"/>
+      <c r="Z72" s="4"/>
+      <c r="AA72" s="7"/>
+      <c r="AB72" s="4"/>
+    </row>
+    <row r="73" spans="1:28" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B73" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="C73" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D73" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="E73" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F73" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G73" s="5">
+        <v>2</v>
+      </c>
+      <c r="H73" s="5">
+        <v>0.23899999999999999</v>
+      </c>
+      <c r="I73" s="5">
+        <v>8.3886000000000002E-2</v>
+      </c>
+      <c r="J73" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K73" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="R73" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="T73" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="X73" s="4"/>
+      <c r="Y73" s="4"/>
+      <c r="Z73" s="4"/>
+      <c r="AA73" s="7"/>
+      <c r="AB73" s="4"/>
+    </row>
+    <row r="74" spans="1:28" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B74" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="C74" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D74" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="E74" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F74" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G74" s="5">
+        <v>3</v>
+      </c>
+      <c r="H74" s="5">
+        <v>0.37330000000000002</v>
+      </c>
+      <c r="I74" s="5">
+        <v>8.1201999999999996E-2</v>
+      </c>
+      <c r="J74" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K74" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="R74" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="T74" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="X74" s="4"/>
+      <c r="Y74" s="4"/>
+      <c r="Z74" s="4"/>
+      <c r="AA74" s="7"/>
+      <c r="AB74" s="4"/>
+    </row>
+    <row r="75" spans="1:28" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B75" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="C75" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D75" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="E75" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F75" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G75" s="5">
+        <v>4</v>
+      </c>
+      <c r="H75" s="5">
+        <v>0.69</v>
+      </c>
+      <c r="I75" s="5">
+        <v>8.0393000000000006E-2</v>
+      </c>
+      <c r="J75" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K75" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="R75" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="T75" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="X75" s="4"/>
+      <c r="Y75" s="4"/>
+      <c r="Z75" s="4"/>
+      <c r="AA75" s="7"/>
+      <c r="AB75" s="4"/>
+    </row>
+    <row r="76" spans="1:28" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B76" s="5" t="s">
+        <v>340</v>
+      </c>
+      <c r="C76" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D76" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="E76" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F76" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G76" s="5">
+        <v>1</v>
+      </c>
+      <c r="H76" s="5">
+        <v>0.18001200000000001</v>
+      </c>
+      <c r="I76" s="5">
+        <v>0.112673</v>
+      </c>
+      <c r="J76" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K76" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="R76" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="T76" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="X76" s="4"/>
+      <c r="Y76" s="4"/>
+      <c r="Z76" s="4"/>
+      <c r="AA76" s="7"/>
+      <c r="AB76" s="4"/>
+    </row>
+    <row r="77" spans="1:28" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B77" s="5" t="s">
+        <v>340</v>
+      </c>
+      <c r="C77" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D77" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="E77" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F77" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G77" s="5">
+        <v>2</v>
+      </c>
+      <c r="H77" s="5">
+        <v>0.25552799999999998</v>
+      </c>
+      <c r="I77" s="5">
+        <v>0.108971</v>
+      </c>
+      <c r="J77" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K77" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="R77" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="T77" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="X77" s="4"/>
+      <c r="Y77" s="4"/>
+      <c r="Z77" s="4"/>
+      <c r="AA77" s="7"/>
+      <c r="AB77" s="4"/>
+    </row>
+    <row r="78" spans="1:28" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B78" s="5" t="s">
+        <v>340</v>
+      </c>
+      <c r="C78" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D78" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="E78" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F78" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G78" s="5">
+        <v>3</v>
+      </c>
+      <c r="H78" s="5">
+        <v>0.41445599999999999</v>
+      </c>
+      <c r="I78" s="5">
+        <v>0.10127</v>
+      </c>
+      <c r="J78" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K78" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="R78" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="T78" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="X78" s="4"/>
+      <c r="Y78" s="4"/>
+      <c r="Z78" s="4"/>
+      <c r="AA78" s="7"/>
+      <c r="AB78" s="4"/>
+    </row>
+    <row r="79" spans="1:28" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B79" s="5" t="s">
+        <v>340</v>
+      </c>
+      <c r="C79" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D79" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="E79" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F79" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G79" s="5">
+        <v>4</v>
+      </c>
+      <c r="H79" s="5">
+        <v>0.67325999999999997</v>
+      </c>
+      <c r="I79" s="5">
+        <v>0.10046099999999999</v>
+      </c>
+      <c r="J79" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K79" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="R79" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="T79" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="X79" s="4"/>
+      <c r="Y79" s="4"/>
+      <c r="Z79" s="4"/>
+      <c r="AA79" s="7"/>
+      <c r="AB79" s="4"/>
+    </row>
+    <row r="80" spans="1:28" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B80" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="C80" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D80" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="E80" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F80" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G80" s="5">
+        <v>1</v>
+      </c>
+      <c r="H80" s="5">
+        <v>0.18215500000000001</v>
+      </c>
+      <c r="I80" s="5">
+        <v>0.114014</v>
+      </c>
+      <c r="J80" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K80" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="R80" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="T80" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="X80" s="4"/>
+      <c r="Y80" s="4"/>
+      <c r="Z80" s="4"/>
+      <c r="AA80" s="7"/>
+      <c r="AB80" s="4"/>
+    </row>
+    <row r="81" spans="1:28" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B81" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="C81" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D81" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="E81" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F81" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G81" s="5">
+        <v>2</v>
+      </c>
+      <c r="H81" s="5">
+        <v>0.25857000000000002</v>
+      </c>
+      <c r="I81" s="5">
+        <v>0.110268</v>
+      </c>
+      <c r="J81" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K81" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="R81" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="T81" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="X81" s="4"/>
+      <c r="Y81" s="4"/>
+      <c r="Z81" s="4"/>
+      <c r="AA81" s="7"/>
+      <c r="AB81" s="4"/>
+    </row>
+    <row r="82" spans="1:28" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B82" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="C82" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D82" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="E82" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F82" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G82" s="5">
+        <v>3</v>
+      </c>
+      <c r="H82" s="5">
+        <v>0.41938999999999999</v>
+      </c>
+      <c r="I82" s="5">
+        <v>0.102476</v>
+      </c>
+      <c r="J82" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K82" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="R82" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="T82" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="X82" s="4"/>
+      <c r="Y82" s="4"/>
+      <c r="Z82" s="4"/>
+      <c r="AA82" s="7"/>
+      <c r="AB82" s="4"/>
+    </row>
+    <row r="83" spans="1:28" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B83" s="5" t="s">
+        <v>341</v>
+      </c>
+      <c r="C83" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D83" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="E83" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F83" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G83" s="5">
+        <v>4</v>
+      </c>
+      <c r="H83" s="5">
+        <v>0.68127499999999996</v>
+      </c>
+      <c r="I83" s="5">
+        <v>0.101657</v>
+      </c>
+      <c r="J83" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K83" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="R83" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="T83" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="X83" s="4"/>
+      <c r="Y83" s="4"/>
+      <c r="Z83" s="4"/>
+      <c r="AA83" s="7"/>
+      <c r="AB83" s="4"/>
+    </row>
+    <row r="84" spans="1:28" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B84" s="5" t="s">
         <v>350</v>
       </c>
-      <c r="C58" s="11" t="s">
+      <c r="C84" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D58" s="11" t="s">
+      <c r="D84" s="5" t="s">
         <v>299</v>
       </c>
-      <c r="E58" s="11" t="s">
-        <v>352</v>
-      </c>
-      <c r="F58" s="11" t="s">
-        <v>346</v>
-      </c>
-      <c r="G58" s="11">
+      <c r="E84" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="F84" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="G84" s="5">
         <v>1</v>
       </c>
-      <c r="H58" s="11">
+      <c r="H84" s="5">
         <v>0.18429799999999999</v>
       </c>
-      <c r="I58" s="11">
+      <c r="I84" s="5">
         <v>0.115355</v>
       </c>
-      <c r="J58" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="K58" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="L58" s="11">
-        <v>3.69</v>
-      </c>
-      <c r="N58" s="11">
-        <v>10</v>
-      </c>
-      <c r="P58" s="11">
-        <v>1.23</v>
-      </c>
-      <c r="R58" s="11" t="s">
+      <c r="J84" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K84" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="R84" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="T58" s="11" t="s">
-        <v>332</v>
-      </c>
-      <c r="X58" s="12"/>
-      <c r="Y58" s="12"/>
-      <c r="Z58" s="12"/>
-      <c r="AA58" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="AB58" s="12"/>
-    </row>
-    <row r="59" spans="1:28" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="11" t="s">
+      <c r="T84" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="X84" s="4"/>
+      <c r="Y84" s="4"/>
+      <c r="Z84" s="4"/>
+      <c r="AA84" s="7"/>
+      <c r="AB84" s="4"/>
+    </row>
+    <row r="85" spans="1:28" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B59" s="11" t="s">
+      <c r="B85" s="5" t="s">
         <v>350</v>
       </c>
-      <c r="C59" s="11" t="s">
+      <c r="C85" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D59" s="11" t="s">
+      <c r="D85" s="5" t="s">
         <v>299</v>
       </c>
-      <c r="E59" s="11" t="s">
-        <v>352</v>
-      </c>
-      <c r="F59" s="11" t="s">
-        <v>346</v>
-      </c>
-      <c r="G59" s="11">
+      <c r="E85" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="F85" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="G85" s="5">
         <v>2</v>
       </c>
-      <c r="H59" s="11">
+      <c r="H85" s="5">
         <v>0.26161200000000001</v>
       </c>
-      <c r="I59" s="11">
+      <c r="I85" s="5">
         <v>0.111565</v>
       </c>
-      <c r="J59" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="K59" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="L59" s="11">
-        <v>3.69</v>
-      </c>
-      <c r="N59" s="11">
-        <v>10</v>
-      </c>
-      <c r="P59" s="11">
-        <v>1.23</v>
-      </c>
-      <c r="R59" s="11" t="s">
+      <c r="J85" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K85" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="R85" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="T59" s="11" t="s">
-        <v>332</v>
-      </c>
-      <c r="X59" s="12"/>
-      <c r="Y59" s="12"/>
-      <c r="Z59" s="12"/>
-      <c r="AA59" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="AB59" s="12"/>
-    </row>
-    <row r="60" spans="1:28" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="11" t="s">
+      <c r="T85" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="X85" s="4"/>
+      <c r="Y85" s="4"/>
+      <c r="Z85" s="4"/>
+      <c r="AA85" s="7"/>
+      <c r="AB85" s="4"/>
+    </row>
+    <row r="86" spans="1:28" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B60" s="11" t="s">
+      <c r="B86" s="5" t="s">
         <v>350</v>
       </c>
-      <c r="C60" s="11" t="s">
+      <c r="C86" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D60" s="11" t="s">
+      <c r="D86" s="5" t="s">
         <v>299</v>
       </c>
-      <c r="E60" s="11" t="s">
-        <v>352</v>
-      </c>
-      <c r="F60" s="11" t="s">
-        <v>346</v>
-      </c>
-      <c r="G60" s="11">
+      <c r="E86" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="F86" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="G86" s="5">
         <v>3</v>
       </c>
-      <c r="H60" s="11">
+      <c r="H86" s="5">
         <v>0.42432399999999998</v>
       </c>
-      <c r="I60" s="11">
+      <c r="I86" s="5">
         <v>0.103682</v>
       </c>
-      <c r="J60" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="K60" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="L60" s="11">
-        <v>3.69</v>
-      </c>
-      <c r="N60" s="11">
-        <v>10</v>
-      </c>
-      <c r="P60" s="11">
-        <v>1.23</v>
-      </c>
-      <c r="R60" s="11" t="s">
+      <c r="J86" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K86" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="R86" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="T60" s="11" t="s">
-        <v>332</v>
-      </c>
-      <c r="X60" s="12"/>
-      <c r="Y60" s="12"/>
-      <c r="Z60" s="12"/>
-      <c r="AA60" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="AB60" s="12"/>
-    </row>
-    <row r="61" spans="1:28" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="11" t="s">
+      <c r="T86" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="X86" s="4"/>
+      <c r="Y86" s="4"/>
+      <c r="Z86" s="4"/>
+      <c r="AA86" s="7"/>
+      <c r="AB86" s="4"/>
+    </row>
+    <row r="87" spans="1:28" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B61" s="11" t="s">
+      <c r="B87" s="5" t="s">
         <v>350</v>
       </c>
-      <c r="C61" s="11" t="s">
+      <c r="C87" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D61" s="11" t="s">
+      <c r="D87" s="5" t="s">
         <v>299</v>
       </c>
-      <c r="E61" s="11" t="s">
-        <v>352</v>
-      </c>
-      <c r="F61" s="11" t="s">
-        <v>346</v>
-      </c>
-      <c r="G61" s="11">
+      <c r="E87" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="F87" s="5" t="s">
+        <v>345</v>
+      </c>
+      <c r="G87" s="5">
         <v>4</v>
       </c>
-      <c r="H61" s="11">
+      <c r="H87" s="5">
         <v>0.68928999999999996</v>
       </c>
-      <c r="I61" s="11">
+      <c r="I87" s="5">
         <v>0.102853</v>
       </c>
-      <c r="J61" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="K61" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="L61" s="11">
-        <v>3.69</v>
-      </c>
-      <c r="N61" s="11">
-        <v>10</v>
-      </c>
-      <c r="P61" s="11">
-        <v>1.23</v>
-      </c>
-      <c r="R61" s="11" t="s">
+      <c r="J87" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K87" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="R87" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="T61" s="11" t="s">
-        <v>332</v>
-      </c>
-      <c r="X61" s="12"/>
-      <c r="Y61" s="12"/>
-      <c r="Z61" s="12"/>
-      <c r="AA61" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="AB61" s="12"/>
-    </row>
-    <row r="62" spans="1:28" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="11" t="s">
+      <c r="T87" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="X87" s="4"/>
+      <c r="Y87" s="4"/>
+      <c r="Z87" s="4"/>
+      <c r="AA87" s="7"/>
+      <c r="AB87" s="4"/>
+    </row>
+    <row r="88" spans="1:28" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B62" s="11" t="s">
-        <v>316</v>
-      </c>
-      <c r="C62" s="11" t="s">
+      <c r="B88" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="C88" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D62" s="11" t="s">
+      <c r="D88" s="5" t="s">
         <v>299</v>
       </c>
-      <c r="E62" s="11" t="s">
+      <c r="E88" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F62" s="11" t="s">
+      <c r="F88" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G62" s="11">
+      <c r="G88" s="5">
         <v>1</v>
       </c>
-      <c r="H62" s="11">
+      <c r="H88" s="5">
         <v>0.1288</v>
       </c>
-      <c r="I62" s="11">
+      <c r="I88" s="5">
         <v>8.5581000000000004E-2</v>
       </c>
-      <c r="J62" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="K62" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="P62" s="11">
-        <v>1.23</v>
-      </c>
-      <c r="R62" s="11" t="s">
+      <c r="J88" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K88" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="R88" s="5" t="s">
         <v>314</v>
       </c>
-      <c r="T62" s="11" t="s">
-        <v>312</v>
-      </c>
-      <c r="X62" s="12"/>
-      <c r="Y62" s="12"/>
-      <c r="Z62" s="12"/>
-      <c r="AA62" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="AB62" s="12"/>
-    </row>
-    <row r="63" spans="1:28" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="11" t="s">
+      <c r="T88" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="X88" s="4"/>
+      <c r="Y88" s="4"/>
+      <c r="Z88" s="4"/>
+      <c r="AA88" s="7"/>
+      <c r="AB88" s="4"/>
+    </row>
+    <row r="89" spans="1:28" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B63" s="11" t="s">
-        <v>316</v>
-      </c>
-      <c r="C63" s="11" t="s">
+      <c r="B89" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="C89" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D63" s="11" t="s">
+      <c r="D89" s="5" t="s">
         <v>299</v>
       </c>
-      <c r="E63" s="11" t="s">
+      <c r="E89" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F63" s="11" t="s">
+      <c r="F89" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G63" s="11">
+      <c r="G89" s="5">
         <v>2</v>
       </c>
-      <c r="H63" s="11">
+      <c r="H89" s="5">
         <v>0.23899999999999999</v>
       </c>
-      <c r="I63" s="11">
+      <c r="I89" s="5">
         <v>8.1878999999999993E-2</v>
       </c>
-      <c r="J63" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="K63" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="P63" s="11">
-        <v>1.23</v>
-      </c>
-      <c r="R63" s="11" t="s">
+      <c r="J89" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K89" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="R89" s="5" t="s">
         <v>314</v>
       </c>
-      <c r="T63" s="11" t="s">
-        <v>312</v>
-      </c>
-      <c r="X63" s="12"/>
-      <c r="Y63" s="12"/>
-      <c r="Z63" s="12"/>
-      <c r="AA63" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="AB63" s="12"/>
-    </row>
-    <row r="64" spans="1:28" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="11" t="s">
+      <c r="T89" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="X89" s="4"/>
+      <c r="Y89" s="4"/>
+      <c r="Z89" s="4"/>
+      <c r="AA89" s="7"/>
+      <c r="AB89" s="4"/>
+    </row>
+    <row r="90" spans="1:28" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B64" s="11" t="s">
-        <v>319</v>
-      </c>
-      <c r="C64" s="11" t="s">
+      <c r="B90" s="5" t="s">
+        <v>347</v>
+      </c>
+      <c r="C90" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="D64" s="11" t="s">
+      <c r="D90" s="5" t="s">
         <v>299</v>
       </c>
-      <c r="E64" s="11" t="s">
+      <c r="E90" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="F64" s="11" t="s">
+      <c r="F90" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="G64" s="11">
+      <c r="G90" s="5">
         <v>1</v>
       </c>
-      <c r="H64" s="11">
+      <c r="H90" s="5">
         <v>0.15165300000000001</v>
       </c>
-      <c r="I64" s="11" t="s">
+      <c r="I90" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="J64" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="K64" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="P64" s="11">
-        <v>1.23</v>
-      </c>
-      <c r="R64" s="11" t="s">
+      <c r="J90" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K90" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="R90" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="T64" s="11" t="s">
-        <v>312</v>
-      </c>
-      <c r="X64" s="12"/>
-      <c r="Y64" s="12"/>
-      <c r="Z64" s="12"/>
-      <c r="AA64" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="AB64" s="12"/>
-    </row>
-    <row r="65" spans="1:28" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="11" t="s">
+      <c r="T90" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="X90" s="4"/>
+      <c r="Y90" s="4"/>
+      <c r="Z90" s="4"/>
+      <c r="AA90" s="7"/>
+      <c r="AB90" s="4"/>
+    </row>
+    <row r="91" spans="1:28" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B65" s="11" t="s">
-        <v>319</v>
-      </c>
-      <c r="C65" s="11" t="s">
+      <c r="B91" s="5" t="s">
+        <v>347</v>
+      </c>
+      <c r="C91" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="D65" s="11" t="s">
+      <c r="D91" s="5" t="s">
         <v>299</v>
       </c>
-      <c r="E65" s="11" t="s">
+      <c r="E91" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="F65" s="11" t="s">
+      <c r="F91" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="G65" s="11">
+      <c r="G91" s="5">
         <v>2</v>
       </c>
-      <c r="H65" s="11">
+      <c r="H91" s="5">
         <v>0.187253</v>
       </c>
-      <c r="I65" s="11" t="s">
+      <c r="I91" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="J65" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="K65" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="P65" s="11">
-        <v>1.23</v>
-      </c>
-      <c r="R65" s="11" t="s">
+      <c r="J91" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K91" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="R91" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="T65" s="11" t="s">
-        <v>312</v>
-      </c>
-      <c r="X65" s="12"/>
-      <c r="Y65" s="12"/>
-      <c r="Z65" s="12"/>
-      <c r="AA65" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="AB65" s="12"/>
-    </row>
-    <row r="66" spans="1:28" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="11" t="s">
+      <c r="T91" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="X91" s="4"/>
+      <c r="Y91" s="4"/>
+      <c r="Z91" s="4"/>
+      <c r="AA91" s="7"/>
+      <c r="AB91" s="4"/>
+    </row>
+    <row r="92" spans="1:28" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B66" s="11" t="s">
-        <v>319</v>
-      </c>
-      <c r="C66" s="11" t="s">
+      <c r="B92" s="5" t="s">
+        <v>347</v>
+      </c>
+      <c r="C92" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="D66" s="11" t="s">
+      <c r="D92" s="5" t="s">
         <v>299</v>
       </c>
-      <c r="E66" s="11" t="s">
+      <c r="E92" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="F66" s="11" t="s">
+      <c r="F92" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="G66" s="11">
+      <c r="G92" s="5">
         <v>3</v>
       </c>
-      <c r="H66" s="11">
+      <c r="H92" s="5">
         <v>0.22175300000000001</v>
       </c>
-      <c r="I66" s="11" t="s">
+      <c r="I92" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="J66" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="K66" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="P66" s="11">
-        <v>1.23</v>
-      </c>
-      <c r="R66" s="11" t="s">
+      <c r="J92" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K92" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="R92" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="T66" s="11" t="s">
-        <v>312</v>
-      </c>
-      <c r="X66" s="12"/>
-      <c r="Y66" s="12"/>
-      <c r="Z66" s="12"/>
-      <c r="AA66" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="AB66" s="12"/>
-    </row>
-    <row r="67" spans="1:28" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="11" t="s">
+      <c r="T92" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="X92" s="4"/>
+      <c r="Y92" s="4"/>
+      <c r="Z92" s="4"/>
+      <c r="AA92" s="7"/>
+      <c r="AB92" s="4"/>
+    </row>
+    <row r="93" spans="1:28" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B67" s="11" t="s">
-        <v>319</v>
-      </c>
-      <c r="C67" s="11" t="s">
+      <c r="B93" s="5" t="s">
+        <v>347</v>
+      </c>
+      <c r="C93" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="D67" s="11" t="s">
+      <c r="D93" s="5" t="s">
         <v>299</v>
       </c>
-      <c r="E67" s="11" t="s">
+      <c r="E93" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="F67" s="11" t="s">
+      <c r="F93" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="G67" s="11">
+      <c r="G93" s="5">
         <v>4</v>
       </c>
-      <c r="H67" s="11">
+      <c r="H93" s="5">
         <v>0.28145300000000001</v>
       </c>
-      <c r="I67" s="11" t="s">
+      <c r="I93" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="J67" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="K67" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="P67" s="11">
-        <v>1.23</v>
-      </c>
-      <c r="R67" s="11" t="s">
+      <c r="J93" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K93" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="R93" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="T67" s="11" t="s">
-        <v>312</v>
-      </c>
-      <c r="X67" s="12"/>
-      <c r="Y67" s="12"/>
-      <c r="Z67" s="12"/>
-      <c r="AA67" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="AB67" s="12"/>
-    </row>
-    <row r="68" spans="1:28" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="11" t="s">
+      <c r="T93" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="X93" s="4"/>
+      <c r="Y93" s="4"/>
+      <c r="Z93" s="4"/>
+      <c r="AA93" s="7"/>
+      <c r="AB93" s="4"/>
+    </row>
+    <row r="94" spans="1:28" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B68" s="11" t="s">
-        <v>317</v>
-      </c>
-      <c r="C68" s="11" t="s">
+      <c r="B94" s="5" t="s">
+        <v>348</v>
+      </c>
+      <c r="C94" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D68" s="11" t="s">
+      <c r="D94" s="5" t="s">
         <v>299</v>
       </c>
-      <c r="E68" s="11" t="s">
+      <c r="E94" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="F68" s="11" t="s">
+      <c r="F94" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="G68" s="11">
+      <c r="G94" s="5">
         <v>1</v>
       </c>
-      <c r="H68" s="11">
+      <c r="H94" s="5">
         <v>0.1646</v>
       </c>
-      <c r="I68" s="11">
+      <c r="I94" s="5">
         <v>9.9929000000000004E-2</v>
       </c>
-      <c r="J68" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="K68" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="P68" s="11">
-        <v>1.23</v>
-      </c>
-      <c r="R68" s="11" t="s">
+      <c r="J94" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K94" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="R94" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="T68" s="11" t="s">
-        <v>313</v>
-      </c>
-      <c r="X68" s="12"/>
-      <c r="Y68" s="12"/>
-      <c r="Z68" s="12"/>
-      <c r="AA68" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="AB68" s="12"/>
-    </row>
-    <row r="69" spans="1:28" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="11" t="s">
+      <c r="T94" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="X94" s="4"/>
+      <c r="Y94" s="4"/>
+      <c r="Z94" s="4"/>
+      <c r="AA94" s="7"/>
+      <c r="AB94" s="4"/>
+    </row>
+    <row r="95" spans="1:28" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B69" s="11" t="s">
-        <v>317</v>
-      </c>
-      <c r="C69" s="11" t="s">
+      <c r="B95" s="5" t="s">
+        <v>348</v>
+      </c>
+      <c r="C95" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D69" s="11" t="s">
+      <c r="D95" s="5" t="s">
         <v>299</v>
       </c>
-      <c r="E69" s="11" t="s">
+      <c r="E95" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="F69" s="11" t="s">
+      <c r="F95" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="G69" s="11">
+      <c r="G95" s="5">
         <v>2</v>
       </c>
-      <c r="H69" s="11">
+      <c r="H95" s="5">
         <v>0.28120000000000001</v>
       </c>
-      <c r="I69" s="11">
+      <c r="I95" s="5">
         <v>9.9173999999999998E-2</v>
       </c>
-      <c r="J69" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="K69" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="P69" s="11">
-        <v>1.23</v>
-      </c>
-      <c r="R69" s="11" t="s">
+      <c r="J95" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K95" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="R95" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="T69" s="11" t="s">
-        <v>313</v>
-      </c>
-      <c r="X69" s="12"/>
-      <c r="Y69" s="12"/>
-      <c r="Z69" s="12"/>
-      <c r="AA69" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="AB69" s="12"/>
-    </row>
-    <row r="70" spans="1:28" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="11" t="s">
+      <c r="T95" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="X95" s="4"/>
+      <c r="Y95" s="4"/>
+      <c r="Z95" s="4"/>
+      <c r="AA95" s="7"/>
+      <c r="AB95" s="4"/>
+    </row>
+    <row r="96" spans="1:28" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B70" s="11" t="s">
-        <v>317</v>
-      </c>
-      <c r="C70" s="11" t="s">
+      <c r="B96" s="5" t="s">
+        <v>348</v>
+      </c>
+      <c r="C96" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D70" s="11" t="s">
+      <c r="D96" s="5" t="s">
         <v>299</v>
       </c>
-      <c r="E70" s="11" t="s">
+      <c r="E96" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="F70" s="11" t="s">
+      <c r="F96" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="G70" s="11">
+      <c r="G96" s="5">
         <v>3</v>
       </c>
-      <c r="H70" s="11">
+      <c r="H96" s="5">
         <v>0.4632</v>
       </c>
-      <c r="I70" s="11">
+      <c r="I96" s="5">
         <v>9.5699000000000006E-2</v>
       </c>
-      <c r="J70" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="K70" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="P70" s="11">
-        <v>1.23</v>
-      </c>
-      <c r="R70" s="11" t="s">
+      <c r="J96" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K96" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="R96" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="T70" s="11" t="s">
-        <v>313</v>
-      </c>
-      <c r="X70" s="12"/>
-      <c r="Y70" s="12"/>
-      <c r="Z70" s="12"/>
-      <c r="AA70" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="AB70" s="12"/>
-    </row>
-    <row r="71" spans="1:28" s="11" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="11" t="s">
+      <c r="T96" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="X96" s="4"/>
+      <c r="Y96" s="4"/>
+      <c r="Z96" s="4"/>
+      <c r="AA96" s="7"/>
+      <c r="AB96" s="4"/>
+    </row>
+    <row r="97" spans="1:28" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B71" s="11" t="s">
-        <v>317</v>
-      </c>
-      <c r="C71" s="11" t="s">
+      <c r="B97" s="5" t="s">
+        <v>348</v>
+      </c>
+      <c r="C97" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D71" s="11" t="s">
+      <c r="D97" s="5" t="s">
         <v>299</v>
       </c>
-      <c r="E71" s="11" t="s">
+      <c r="E97" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="F71" s="11" t="s">
+      <c r="F97" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="G71" s="11">
+      <c r="G97" s="5">
         <v>4</v>
       </c>
-      <c r="H71" s="11">
+      <c r="H97" s="5">
         <v>0.91469999999999996</v>
       </c>
-      <c r="I71" s="11">
+      <c r="I97" s="5">
         <v>9.4269000000000006E-2</v>
       </c>
-      <c r="J71" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="K71" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="P71" s="11">
-        <v>1.23</v>
-      </c>
-      <c r="R71" s="11" t="s">
+      <c r="J97" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K97" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="R97" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="T71" s="11" t="s">
-        <v>313</v>
-      </c>
-      <c r="X71" s="12"/>
-      <c r="Y71" s="12"/>
-      <c r="Z71" s="12"/>
-      <c r="AA71" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="AB71" s="12"/>
-    </row>
-    <row r="72" spans="1:28" s="14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="B72" s="14" t="s">
-        <v>339</v>
-      </c>
-      <c r="C72" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="D72" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="E72" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="F72" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="G72" s="14">
-        <v>1</v>
-      </c>
-      <c r="H72" s="14">
-        <v>0.14419999999999999</v>
-      </c>
-      <c r="I72" s="14">
-        <v>8.4075999999999998E-2</v>
-      </c>
-      <c r="J72" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="K72" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="R72" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="T72" s="14" t="s">
-        <v>343</v>
-      </c>
-      <c r="X72" s="15"/>
-      <c r="Y72" s="15"/>
-      <c r="Z72" s="15"/>
-      <c r="AA72" s="16"/>
-      <c r="AB72" s="15"/>
-    </row>
-    <row r="73" spans="1:28" s="14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="B73" s="14" t="s">
-        <v>339</v>
-      </c>
-      <c r="C73" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="D73" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="E73" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="F73" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="G73" s="14">
-        <v>2</v>
-      </c>
-      <c r="H73" s="14">
-        <v>0.23899999999999999</v>
-      </c>
-      <c r="I73" s="14">
-        <v>8.3886000000000002E-2</v>
-      </c>
-      <c r="J73" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="K73" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="R73" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="T73" s="14" t="s">
-        <v>343</v>
-      </c>
-      <c r="X73" s="15"/>
-      <c r="Y73" s="15"/>
-      <c r="Z73" s="15"/>
-      <c r="AA73" s="16"/>
-      <c r="AB73" s="15"/>
-    </row>
-    <row r="74" spans="1:28" s="14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="B74" s="14" t="s">
-        <v>339</v>
-      </c>
-      <c r="C74" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="D74" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="E74" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="F74" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="G74" s="14">
-        <v>3</v>
-      </c>
-      <c r="H74" s="14">
-        <v>0.37330000000000002</v>
-      </c>
-      <c r="I74" s="14">
-        <v>8.1201999999999996E-2</v>
-      </c>
-      <c r="J74" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="K74" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="R74" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="T74" s="14" t="s">
-        <v>343</v>
-      </c>
-      <c r="X74" s="15"/>
-      <c r="Y74" s="15"/>
-      <c r="Z74" s="15"/>
-      <c r="AA74" s="16"/>
-      <c r="AB74" s="15"/>
-    </row>
-    <row r="75" spans="1:28" s="14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="B75" s="14" t="s">
-        <v>339</v>
-      </c>
-      <c r="C75" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="D75" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="E75" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="F75" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="G75" s="14">
-        <v>4</v>
-      </c>
-      <c r="H75" s="14">
-        <v>0.69</v>
-      </c>
-      <c r="I75" s="14">
-        <v>8.0393000000000006E-2</v>
-      </c>
-      <c r="J75" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="K75" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="R75" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="T75" s="14" t="s">
-        <v>343</v>
-      </c>
-      <c r="X75" s="15"/>
-      <c r="Y75" s="15"/>
-      <c r="Z75" s="15"/>
-      <c r="AA75" s="16"/>
-      <c r="AB75" s="15"/>
-    </row>
-    <row r="76" spans="1:28" s="14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="B76" s="14" t="s">
-        <v>340</v>
-      </c>
-      <c r="C76" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="D76" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="E76" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="F76" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="G76" s="14">
-        <v>1</v>
-      </c>
-      <c r="H76" s="14">
-        <v>0.18001200000000001</v>
-      </c>
-      <c r="I76" s="14">
-        <v>0.112673</v>
-      </c>
-      <c r="J76" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="K76" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="L76" s="14">
-        <v>3.69</v>
-      </c>
-      <c r="N76" s="14">
-        <v>10</v>
-      </c>
-      <c r="R76" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="T76" s="14" t="s">
+      <c r="T97" s="5" t="s">
         <v>344</v>
       </c>
-      <c r="X76" s="15"/>
-      <c r="Y76" s="15"/>
-      <c r="Z76" s="15"/>
-      <c r="AA76" s="16"/>
-      <c r="AB76" s="15"/>
-    </row>
-    <row r="77" spans="1:28" s="14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="B77" s="14" t="s">
-        <v>340</v>
-      </c>
-      <c r="C77" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="D77" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="E77" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="F77" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="G77" s="14">
-        <v>2</v>
-      </c>
-      <c r="H77" s="14">
-        <v>0.25552799999999998</v>
-      </c>
-      <c r="I77" s="14">
-        <v>0.108971</v>
-      </c>
-      <c r="J77" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="K77" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="L77" s="14">
-        <v>3.69</v>
-      </c>
-      <c r="N77" s="14">
-        <v>10</v>
-      </c>
-      <c r="R77" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="T77" s="14" t="s">
-        <v>344</v>
-      </c>
-      <c r="X77" s="15"/>
-      <c r="Y77" s="15"/>
-      <c r="Z77" s="15"/>
-      <c r="AA77" s="16"/>
-      <c r="AB77" s="15"/>
-    </row>
-    <row r="78" spans="1:28" s="14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="B78" s="14" t="s">
-        <v>340</v>
-      </c>
-      <c r="C78" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="D78" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="E78" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="F78" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="G78" s="14">
-        <v>3</v>
-      </c>
-      <c r="H78" s="14">
-        <v>0.41445599999999999</v>
-      </c>
-      <c r="I78" s="14">
-        <v>0.10127</v>
-      </c>
-      <c r="J78" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="K78" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="L78" s="14">
-        <v>3.69</v>
-      </c>
-      <c r="N78" s="14">
-        <v>10</v>
-      </c>
-      <c r="R78" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="T78" s="14" t="s">
-        <v>344</v>
-      </c>
-      <c r="X78" s="15"/>
-      <c r="Y78" s="15"/>
-      <c r="Z78" s="15"/>
-      <c r="AA78" s="16"/>
-      <c r="AB78" s="15"/>
-    </row>
-    <row r="79" spans="1:28" s="14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="B79" s="14" t="s">
-        <v>340</v>
-      </c>
-      <c r="C79" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="D79" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="E79" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="F79" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="G79" s="14">
-        <v>4</v>
-      </c>
-      <c r="H79" s="14">
-        <v>0.67325999999999997</v>
-      </c>
-      <c r="I79" s="14">
-        <v>0.10046099999999999</v>
-      </c>
-      <c r="J79" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="K79" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="L79" s="14">
-        <v>3.69</v>
-      </c>
-      <c r="N79" s="14">
-        <v>10</v>
-      </c>
-      <c r="R79" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="T79" s="14" t="s">
-        <v>344</v>
-      </c>
-      <c r="X79" s="15"/>
-      <c r="Y79" s="15"/>
-      <c r="Z79" s="15"/>
-      <c r="AA79" s="16"/>
-      <c r="AB79" s="15"/>
-    </row>
-    <row r="80" spans="1:28" s="14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="B80" s="14" t="s">
-        <v>341</v>
-      </c>
-      <c r="C80" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="D80" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="E80" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F80" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="G80" s="14">
-        <v>1</v>
-      </c>
-      <c r="H80" s="14">
-        <v>0.18215500000000001</v>
-      </c>
-      <c r="I80" s="14">
-        <v>0.114014</v>
-      </c>
-      <c r="J80" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="K80" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="L80" s="14">
-        <v>3.69</v>
-      </c>
-      <c r="N80" s="14">
-        <v>10</v>
-      </c>
-      <c r="R80" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="T80" s="14" t="s">
-        <v>344</v>
-      </c>
-      <c r="X80" s="15"/>
-      <c r="Y80" s="15"/>
-      <c r="Z80" s="15"/>
-      <c r="AA80" s="16"/>
-      <c r="AB80" s="15"/>
-    </row>
-    <row r="81" spans="1:28" s="14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="B81" s="14" t="s">
-        <v>341</v>
-      </c>
-      <c r="C81" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="D81" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="E81" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F81" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="G81" s="14">
-        <v>2</v>
-      </c>
-      <c r="H81" s="14">
-        <v>0.25857000000000002</v>
-      </c>
-      <c r="I81" s="14">
-        <v>0.110268</v>
-      </c>
-      <c r="J81" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="K81" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="L81" s="14">
-        <v>3.69</v>
-      </c>
-      <c r="N81" s="14">
-        <v>10</v>
-      </c>
-      <c r="R81" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="T81" s="14" t="s">
-        <v>344</v>
-      </c>
-      <c r="X81" s="15"/>
-      <c r="Y81" s="15"/>
-      <c r="Z81" s="15"/>
-      <c r="AA81" s="16"/>
-      <c r="AB81" s="15"/>
-    </row>
-    <row r="82" spans="1:28" s="14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="B82" s="14" t="s">
-        <v>341</v>
-      </c>
-      <c r="C82" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="D82" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="E82" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F82" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="G82" s="14">
-        <v>3</v>
-      </c>
-      <c r="H82" s="14">
-        <v>0.41938999999999999</v>
-      </c>
-      <c r="I82" s="14">
-        <v>0.102476</v>
-      </c>
-      <c r="J82" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="K82" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="L82" s="14">
-        <v>3.69</v>
-      </c>
-      <c r="N82" s="14">
-        <v>10</v>
-      </c>
-      <c r="R82" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="T82" s="14" t="s">
-        <v>344</v>
-      </c>
-      <c r="X82" s="15"/>
-      <c r="Y82" s="15"/>
-      <c r="Z82" s="15"/>
-      <c r="AA82" s="16"/>
-      <c r="AB82" s="15"/>
-    </row>
-    <row r="83" spans="1:28" s="14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="B83" s="14" t="s">
-        <v>341</v>
-      </c>
-      <c r="C83" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="D83" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="E83" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F83" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="G83" s="14">
-        <v>4</v>
-      </c>
-      <c r="H83" s="14">
-        <v>0.68127499999999996</v>
-      </c>
-      <c r="I83" s="14">
-        <v>0.101657</v>
-      </c>
-      <c r="J83" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="K83" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="L83" s="14">
-        <v>3.69</v>
-      </c>
-      <c r="N83" s="14">
-        <v>10</v>
-      </c>
-      <c r="R83" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="T83" s="14" t="s">
-        <v>344</v>
-      </c>
-      <c r="X83" s="15"/>
-      <c r="Y83" s="15"/>
-      <c r="Z83" s="15"/>
-      <c r="AA83" s="16"/>
-      <c r="AB83" s="15"/>
-    </row>
-    <row r="84" spans="1:28" s="14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="B84" s="14" t="s">
-        <v>351</v>
-      </c>
-      <c r="C84" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="D84" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="E84" s="14" t="s">
-        <v>352</v>
-      </c>
-      <c r="F84" s="14" t="s">
-        <v>346</v>
-      </c>
-      <c r="G84" s="14">
-        <v>1</v>
-      </c>
-      <c r="H84" s="14">
-        <v>0.18429799999999999</v>
-      </c>
-      <c r="I84" s="14">
-        <v>0.115355</v>
-      </c>
-      <c r="J84" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="K84" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="L84" s="14">
-        <v>3.69</v>
-      </c>
-      <c r="N84" s="14">
-        <v>10</v>
-      </c>
-      <c r="R84" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="T84" s="14" t="s">
-        <v>344</v>
-      </c>
-      <c r="X84" s="15"/>
-      <c r="Y84" s="15"/>
-      <c r="Z84" s="15"/>
-      <c r="AA84" s="16"/>
-      <c r="AB84" s="15"/>
-    </row>
-    <row r="85" spans="1:28" s="14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="B85" s="14" t="s">
-        <v>351</v>
-      </c>
-      <c r="C85" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="D85" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="E85" s="14" t="s">
-        <v>352</v>
-      </c>
-      <c r="F85" s="14" t="s">
-        <v>346</v>
-      </c>
-      <c r="G85" s="14">
-        <v>2</v>
-      </c>
-      <c r="H85" s="14">
-        <v>0.26161200000000001</v>
-      </c>
-      <c r="I85" s="14">
-        <v>0.111565</v>
-      </c>
-      <c r="J85" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="K85" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="L85" s="14">
-        <v>3.69</v>
-      </c>
-      <c r="N85" s="14">
-        <v>10</v>
-      </c>
-      <c r="R85" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="T85" s="14" t="s">
-        <v>344</v>
-      </c>
-      <c r="X85" s="15"/>
-      <c r="Y85" s="15"/>
-      <c r="Z85" s="15"/>
-      <c r="AA85" s="16"/>
-      <c r="AB85" s="15"/>
-    </row>
-    <row r="86" spans="1:28" s="14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="B86" s="14" t="s">
-        <v>351</v>
-      </c>
-      <c r="C86" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="D86" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="E86" s="14" t="s">
-        <v>352</v>
-      </c>
-      <c r="F86" s="14" t="s">
-        <v>346</v>
-      </c>
-      <c r="G86" s="14">
-        <v>3</v>
-      </c>
-      <c r="H86" s="14">
-        <v>0.42432399999999998</v>
-      </c>
-      <c r="I86" s="14">
-        <v>0.103682</v>
-      </c>
-      <c r="J86" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="K86" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="L86" s="14">
-        <v>3.69</v>
-      </c>
-      <c r="N86" s="14">
-        <v>10</v>
-      </c>
-      <c r="R86" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="T86" s="14" t="s">
-        <v>344</v>
-      </c>
-      <c r="X86" s="15"/>
-      <c r="Y86" s="15"/>
-      <c r="Z86" s="15"/>
-      <c r="AA86" s="16"/>
-      <c r="AB86" s="15"/>
-    </row>
-    <row r="87" spans="1:28" s="14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="B87" s="14" t="s">
-        <v>351</v>
-      </c>
-      <c r="C87" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="D87" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="E87" s="14" t="s">
-        <v>352</v>
-      </c>
-      <c r="F87" s="14" t="s">
-        <v>346</v>
-      </c>
-      <c r="G87" s="14">
-        <v>4</v>
-      </c>
-      <c r="H87" s="14">
-        <v>0.68928999999999996</v>
-      </c>
-      <c r="I87" s="14">
-        <v>0.102853</v>
-      </c>
-      <c r="J87" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="K87" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="L87" s="14">
-        <v>3.69</v>
-      </c>
-      <c r="N87" s="14">
-        <v>10</v>
-      </c>
-      <c r="R87" s="14" t="s">
-        <v>40</v>
-      </c>
-      <c r="T87" s="14" t="s">
-        <v>344</v>
-      </c>
-      <c r="X87" s="15"/>
-      <c r="Y87" s="15"/>
-      <c r="Z87" s="15"/>
-      <c r="AA87" s="16"/>
-      <c r="AB87" s="15"/>
-    </row>
-    <row r="88" spans="1:28" s="14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="B88" s="14" t="s">
-        <v>342</v>
-      </c>
-      <c r="C88" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="D88" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="E88" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="F88" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="G88" s="14">
-        <v>1</v>
-      </c>
-      <c r="H88" s="14">
-        <v>0.1288</v>
-      </c>
-      <c r="I88" s="14">
-        <v>8.5581000000000004E-2</v>
-      </c>
-      <c r="J88" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="K88" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="R88" s="14" t="s">
-        <v>314</v>
-      </c>
-      <c r="T88" s="14" t="s">
-        <v>343</v>
-      </c>
-      <c r="X88" s="15"/>
-      <c r="Y88" s="15"/>
-      <c r="Z88" s="15"/>
-      <c r="AA88" s="16"/>
-      <c r="AB88" s="15"/>
-    </row>
-    <row r="89" spans="1:28" s="14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="B89" s="14" t="s">
-        <v>342</v>
-      </c>
-      <c r="C89" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="D89" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="E89" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="F89" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="G89" s="14">
-        <v>2</v>
-      </c>
-      <c r="H89" s="14">
-        <v>0.23899999999999999</v>
-      </c>
-      <c r="I89" s="14">
-        <v>8.1878999999999993E-2</v>
-      </c>
-      <c r="J89" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="K89" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="R89" s="14" t="s">
-        <v>314</v>
-      </c>
-      <c r="T89" s="14" t="s">
-        <v>343</v>
-      </c>
-      <c r="X89" s="15"/>
-      <c r="Y89" s="15"/>
-      <c r="Z89" s="15"/>
-      <c r="AA89" s="16"/>
-      <c r="AB89" s="15"/>
-    </row>
-    <row r="90" spans="1:28" s="14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="B90" s="14" t="s">
-        <v>348</v>
-      </c>
-      <c r="C90" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="D90" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="E90" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F90" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="G90" s="14">
-        <v>1</v>
-      </c>
-      <c r="H90" s="14">
-        <v>0.15165300000000001</v>
-      </c>
-      <c r="I90" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="J90" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="K90" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="R90" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="T90" s="14" t="s">
-        <v>343</v>
-      </c>
-      <c r="X90" s="15"/>
-      <c r="Y90" s="15"/>
-      <c r="Z90" s="15"/>
-      <c r="AA90" s="16"/>
-      <c r="AB90" s="15"/>
-    </row>
-    <row r="91" spans="1:28" s="14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="B91" s="14" t="s">
-        <v>348</v>
-      </c>
-      <c r="C91" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="D91" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="E91" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F91" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="G91" s="14">
-        <v>2</v>
-      </c>
-      <c r="H91" s="14">
-        <v>0.187253</v>
-      </c>
-      <c r="I91" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="J91" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="K91" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="R91" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="T91" s="14" t="s">
-        <v>343</v>
-      </c>
-      <c r="X91" s="15"/>
-      <c r="Y91" s="15"/>
-      <c r="Z91" s="15"/>
-      <c r="AA91" s="16"/>
-      <c r="AB91" s="15"/>
-    </row>
-    <row r="92" spans="1:28" s="14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="B92" s="14" t="s">
-        <v>348</v>
-      </c>
-      <c r="C92" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="D92" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="E92" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F92" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="G92" s="14">
-        <v>3</v>
-      </c>
-      <c r="H92" s="14">
-        <v>0.22175300000000001</v>
-      </c>
-      <c r="I92" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="J92" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="K92" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="R92" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="T92" s="14" t="s">
-        <v>343</v>
-      </c>
-      <c r="X92" s="15"/>
-      <c r="Y92" s="15"/>
-      <c r="Z92" s="15"/>
-      <c r="AA92" s="16"/>
-      <c r="AB92" s="15"/>
-    </row>
-    <row r="93" spans="1:28" s="14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="B93" s="14" t="s">
-        <v>348</v>
-      </c>
-      <c r="C93" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="D93" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="E93" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F93" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="G93" s="14">
-        <v>4</v>
-      </c>
-      <c r="H93" s="14">
-        <v>0.28145300000000001</v>
-      </c>
-      <c r="I93" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="J93" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="K93" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="R93" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="T93" s="14" t="s">
-        <v>343</v>
-      </c>
-      <c r="X93" s="15"/>
-      <c r="Y93" s="15"/>
-      <c r="Z93" s="15"/>
-      <c r="AA93" s="16"/>
-      <c r="AB93" s="15"/>
-    </row>
-    <row r="94" spans="1:28" s="14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="B94" s="14" t="s">
-        <v>349</v>
-      </c>
-      <c r="C94" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="D94" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="E94" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F94" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="G94" s="14">
-        <v>1</v>
-      </c>
-      <c r="H94" s="14">
-        <v>0.1646</v>
-      </c>
-      <c r="I94" s="14">
-        <v>9.9929000000000004E-2</v>
-      </c>
-      <c r="J94" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="K94" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="R94" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="T94" s="14" t="s">
-        <v>345</v>
-      </c>
-      <c r="X94" s="15"/>
-      <c r="Y94" s="15"/>
-      <c r="Z94" s="15"/>
-      <c r="AA94" s="16"/>
-      <c r="AB94" s="15"/>
-    </row>
-    <row r="95" spans="1:28" s="14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="B95" s="14" t="s">
-        <v>349</v>
-      </c>
-      <c r="C95" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="D95" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="E95" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F95" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="G95" s="14">
-        <v>2</v>
-      </c>
-      <c r="H95" s="14">
-        <v>0.28120000000000001</v>
-      </c>
-      <c r="I95" s="14">
-        <v>9.9173999999999998E-2</v>
-      </c>
-      <c r="J95" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="K95" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="R95" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="T95" s="14" t="s">
-        <v>345</v>
-      </c>
-      <c r="X95" s="15"/>
-      <c r="Y95" s="15"/>
-      <c r="Z95" s="15"/>
-      <c r="AA95" s="16"/>
-      <c r="AB95" s="15"/>
-    </row>
-    <row r="96" spans="1:28" s="14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="B96" s="14" t="s">
-        <v>349</v>
-      </c>
-      <c r="C96" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="D96" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="E96" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F96" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="G96" s="14">
-        <v>3</v>
-      </c>
-      <c r="H96" s="14">
-        <v>0.4632</v>
-      </c>
-      <c r="I96" s="14">
-        <v>9.5699000000000006E-2</v>
-      </c>
-      <c r="J96" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="K96" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="R96" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="T96" s="14" t="s">
-        <v>345</v>
-      </c>
-      <c r="X96" s="15"/>
-      <c r="Y96" s="15"/>
-      <c r="Z96" s="15"/>
-      <c r="AA96" s="16"/>
-      <c r="AB96" s="15"/>
-    </row>
-    <row r="97" spans="1:28" s="14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="B97" s="14" t="s">
-        <v>349</v>
-      </c>
-      <c r="C97" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="D97" s="14" t="s">
-        <v>299</v>
-      </c>
-      <c r="E97" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="F97" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="G97" s="14">
-        <v>4</v>
-      </c>
-      <c r="H97" s="14">
-        <v>0.91469999999999996</v>
-      </c>
-      <c r="I97" s="14">
-        <v>9.4269000000000006E-2</v>
-      </c>
-      <c r="J97" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="K97" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="R97" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="T97" s="14" t="s">
-        <v>345</v>
-      </c>
-      <c r="X97" s="15"/>
-      <c r="Y97" s="15"/>
-      <c r="Z97" s="15"/>
-      <c r="AA97" s="16"/>
-      <c r="AB97" s="15"/>
+      <c r="X97" s="4"/>
+      <c r="Y97" s="4"/>
+      <c r="Z97" s="4"/>
+      <c r="AA97" s="7"/>
+      <c r="AB97" s="4"/>
     </row>
     <row r="98" spans="1:28" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A98" s="5" t="s">
@@ -6462,7 +6373,7 @@
         <v>43</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C102" s="5" t="s">
         <v>16</v>
@@ -6474,7 +6385,7 @@
         <v>18</v>
       </c>
       <c r="F102" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G102" s="5">
         <v>1</v>
@@ -6505,7 +6416,7 @@
         <v>43</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C103" s="5" t="s">
         <v>16</v>
@@ -6517,7 +6428,7 @@
         <v>18</v>
       </c>
       <c r="F103" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G103" s="5">
         <v>2</v>
@@ -6548,7 +6459,7 @@
         <v>43</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C104" s="5" t="s">
         <v>16</v>
@@ -6560,7 +6471,7 @@
         <v>18</v>
       </c>
       <c r="F104" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G104" s="5">
         <v>3</v>
@@ -6591,7 +6502,7 @@
         <v>43</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C105" s="5" t="s">
         <v>16</v>
@@ -6603,7 +6514,7 @@
         <v>18</v>
       </c>
       <c r="F105" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G105" s="5">
         <v>4</v>
@@ -6634,7 +6545,7 @@
         <v>43</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C106" s="5" t="s">
         <v>16</v>
@@ -6677,7 +6588,7 @@
         <v>43</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C107" s="5" t="s">
         <v>16</v>
@@ -6720,7 +6631,7 @@
         <v>43</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C108" s="5" t="s">
         <v>16</v>
@@ -6763,7 +6674,7 @@
         <v>43</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C109" s="5" t="s">
         <v>16</v>
@@ -7863,10 +7774,10 @@
         <v>299</v>
       </c>
       <c r="E134" s="5" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F134" s="5" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G134" s="5">
         <v>1</v>
@@ -7906,10 +7817,10 @@
         <v>299</v>
       </c>
       <c r="E135" s="5" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F135" s="5" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G135" s="5">
         <v>2</v>
@@ -7949,10 +7860,10 @@
         <v>299</v>
       </c>
       <c r="E136" s="5" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F136" s="5" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G136" s="5">
         <v>3</v>
@@ -7992,10 +7903,10 @@
         <v>299</v>
       </c>
       <c r="E137" s="5" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F137" s="5" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G137" s="5">
         <v>4</v>
@@ -8542,7 +8453,7 @@
         <v>49</v>
       </c>
       <c r="B150" s="5" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C150" s="5" t="s">
         <v>16</v>
@@ -8551,10 +8462,10 @@
         <v>17</v>
       </c>
       <c r="E150" s="5" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F150" s="5" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G150" s="5">
         <v>1</v>
@@ -8585,7 +8496,7 @@
         <v>49</v>
       </c>
       <c r="B151" s="5" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C151" s="5" t="s">
         <v>16</v>
@@ -8594,10 +8505,10 @@
         <v>17</v>
       </c>
       <c r="E151" s="5" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F151" s="5" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G151" s="5">
         <v>2</v>
@@ -8628,7 +8539,7 @@
         <v>49</v>
       </c>
       <c r="B152" s="5" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C152" s="5" t="s">
         <v>16</v>
@@ -8637,10 +8548,10 @@
         <v>17</v>
       </c>
       <c r="E152" s="5" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F152" s="5" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G152" s="5">
         <v>3</v>
@@ -8671,7 +8582,7 @@
         <v>49</v>
       </c>
       <c r="B153" s="5" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C153" s="5" t="s">
         <v>16</v>
@@ -8680,10 +8591,10 @@
         <v>17</v>
       </c>
       <c r="E153" s="5" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F153" s="5" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G153" s="5">
         <v>4</v>
@@ -8714,7 +8625,7 @@
         <v>49</v>
       </c>
       <c r="B154" s="5" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C154" s="5" t="s">
         <v>16</v>
@@ -8757,7 +8668,7 @@
         <v>49</v>
       </c>
       <c r="B155" s="5" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C155" s="5" t="s">
         <v>16</v>
@@ -8800,7 +8711,7 @@
         <v>49</v>
       </c>
       <c r="B156" s="5" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C156" s="5" t="s">
         <v>16</v>
@@ -8843,7 +8754,7 @@
         <v>49</v>
       </c>
       <c r="B157" s="5" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C157" s="5" t="s">
         <v>16</v>
@@ -8886,7 +8797,7 @@
         <v>49</v>
       </c>
       <c r="B158" s="5" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C158" s="5" t="s">
         <v>16</v>
@@ -8929,7 +8840,7 @@
         <v>49</v>
       </c>
       <c r="B159" s="5" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C159" s="5" t="s">
         <v>16</v>
@@ -8972,7 +8883,7 @@
         <v>49</v>
       </c>
       <c r="B160" s="5" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C160" s="5" t="s">
         <v>16</v>
@@ -9015,7 +8926,7 @@
         <v>49</v>
       </c>
       <c r="B161" s="5" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C161" s="5" t="s">
         <v>16</v>
@@ -9058,7 +8969,7 @@
         <v>49</v>
       </c>
       <c r="B162" s="5" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C162" s="5" t="s">
         <v>16</v>
@@ -9067,10 +8978,10 @@
         <v>301</v>
       </c>
       <c r="E162" s="5" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F162" s="5" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G162" s="5">
         <v>1</v>
@@ -9101,7 +9012,7 @@
         <v>49</v>
       </c>
       <c r="B163" s="5" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C163" s="5" t="s">
         <v>16</v>
@@ -9110,10 +9021,10 @@
         <v>301</v>
       </c>
       <c r="E163" s="5" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F163" s="5" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G163" s="5">
         <v>2</v>
@@ -9144,7 +9055,7 @@
         <v>49</v>
       </c>
       <c r="B164" s="5" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C164" s="5" t="s">
         <v>16</v>
@@ -9153,10 +9064,10 @@
         <v>301</v>
       </c>
       <c r="E164" s="5" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F164" s="5" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G164" s="5">
         <v>3</v>
@@ -9187,7 +9098,7 @@
         <v>49</v>
       </c>
       <c r="B165" s="5" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C165" s="5" t="s">
         <v>16</v>
@@ -9196,10 +9107,10 @@
         <v>301</v>
       </c>
       <c r="E165" s="5" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F165" s="5" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G165" s="5">
         <v>4</v>
@@ -9230,7 +9141,7 @@
         <v>49</v>
       </c>
       <c r="B166" s="5" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C166" s="5" t="s">
         <v>16</v>
@@ -9273,7 +9184,7 @@
         <v>49</v>
       </c>
       <c r="B167" s="5" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C167" s="5" t="s">
         <v>16</v>
@@ -9316,7 +9227,7 @@
         <v>49</v>
       </c>
       <c r="B168" s="5" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C168" s="5" t="s">
         <v>16</v>
@@ -9359,7 +9270,7 @@
         <v>49</v>
       </c>
       <c r="B169" s="5" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C169" s="5" t="s">
         <v>16</v>
@@ -9402,7 +9313,7 @@
         <v>49</v>
       </c>
       <c r="B170" s="5" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C170" s="5" t="s">
         <v>16</v>
@@ -9445,7 +9356,7 @@
         <v>49</v>
       </c>
       <c r="B171" s="5" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C171" s="5" t="s">
         <v>16</v>
@@ -9488,7 +9399,7 @@
         <v>49</v>
       </c>
       <c r="B172" s="5" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C172" s="5" t="s">
         <v>16</v>
@@ -9531,7 +9442,7 @@
         <v>49</v>
       </c>
       <c r="B173" s="5" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C173" s="5" t="s">
         <v>16</v>
@@ -9918,7 +9829,7 @@
         <v>55</v>
       </c>
       <c r="B182" s="5" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C182" s="5" t="s">
         <v>16</v>
@@ -9961,7 +9872,7 @@
         <v>55</v>
       </c>
       <c r="B183" s="5" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C183" s="5" t="s">
         <v>16</v>
@@ -10004,7 +9915,7 @@
         <v>55</v>
       </c>
       <c r="B184" s="5" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C184" s="5" t="s">
         <v>16</v>
@@ -10047,7 +9958,7 @@
         <v>55</v>
       </c>
       <c r="B185" s="5" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C185" s="5" t="s">
         <v>16</v>
@@ -10090,7 +10001,7 @@
         <v>55</v>
       </c>
       <c r="B186" s="5" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C186" s="5" t="s">
         <v>16</v>
@@ -10133,7 +10044,7 @@
         <v>55</v>
       </c>
       <c r="B187" s="5" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C187" s="5" t="s">
         <v>16</v>
@@ -10176,7 +10087,7 @@
         <v>55</v>
       </c>
       <c r="B188" s="5" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C188" s="5" t="s">
         <v>16</v>
@@ -10219,7 +10130,7 @@
         <v>55</v>
       </c>
       <c r="B189" s="5" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C189" s="5" t="s">
         <v>16</v>
@@ -10262,7 +10173,7 @@
         <v>55</v>
       </c>
       <c r="B190" s="5" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C190" s="5" t="s">
         <v>16</v>
@@ -10305,7 +10216,7 @@
         <v>55</v>
       </c>
       <c r="B191" s="5" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C191" s="5" t="s">
         <v>16</v>
@@ -10348,7 +10259,7 @@
         <v>55</v>
       </c>
       <c r="B192" s="5" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C192" s="5" t="s">
         <v>16</v>
@@ -10391,7 +10302,7 @@
         <v>55</v>
       </c>
       <c r="B193" s="5" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C193" s="5" t="s">
         <v>16</v>
@@ -10437,7 +10348,7 @@
       <c r="AB194" s="4"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AB1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:AB193" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/data/simuladores/simulador-tarifarios-gas/tarifarios_gas_natural_Tiago_Felicia.xlsx
+++ b/data/simuladores/simulador-tarifarios-gas/tarifarios_gas_natural_Tiago_Felicia.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tiago\Downloads\Claude Code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67E7AA2F-58C4-49D5-99C6-02773A7ABE75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A3B7522-C1B4-4A12-B482-A726184379CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tarifas_Gas_Master" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2680" uniqueCount="376">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2824" uniqueCount="382">
   <si>
     <t>Comercializador</t>
   </si>
@@ -951,12 +951,6 @@
     <t>https://www.edp.pt/empresas/energia/gas-eletricidade-negocios/</t>
   </si>
   <si>
-    <t>Galp | Galp Negócios Gas Natural</t>
-  </si>
-  <si>
-    <t>Galp | Galp Negócios Gas Natural | DD</t>
-  </si>
-  <si>
     <t>https://www.galp.com/pt/casa/planos-eletricidade-e-gas/negocios/eletricidade-empresas</t>
   </si>
   <si>
@@ -1168,6 +1162,30 @@
   </si>
   <si>
     <t>https://www.endesa.pt/content/dam/endesa-pt/campanhas/Regulamento-Campanha-Bem-Vindo-Quero-Mais.pdf</t>
+  </si>
+  <si>
+    <t>Repsol</t>
+  </si>
+  <si>
+    <t>Repsol | VIVA+ | Gás Natural · (-15%) | DD + FE</t>
+  </si>
+  <si>
+    <t>https://www.repsol.pt/particulares/casa/eletricidade-gas/planos-eletricidade-e-gas/</t>
+  </si>
+  <si>
+    <t>Repsol | VIVA+ | Gás Natural · (-13%) | DD</t>
+  </si>
+  <si>
+    <t>Repsol | VIVA+ | Gás Natural · (-7%) | FE</t>
+  </si>
+  <si>
+    <t>Repsol | VIVA+ | Gás Natural · (-5%)</t>
+  </si>
+  <si>
+    <t>Galp | Galp Negócios Gás Natural | DD</t>
+  </si>
+  <si>
+    <t>Galp | Galp Negócios Gás Natural</t>
   </si>
 </sst>
 </file>
@@ -1272,7 +1290,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1290,11 +1308,6 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1630,7 +1643,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AG198"/>
+  <dimension ref="A1:AG213"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16.90625" bestFit="1" customWidth="1"/>
@@ -1705,25 +1718,25 @@
         <v>11</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="N1" s="4" t="s">
         <v>12</v>
       </c>
       <c r="O1" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="Q1" s="4" t="s">
         <v>308</v>
-      </c>
-      <c r="P1" s="4" t="s">
-        <v>309</v>
-      </c>
-      <c r="Q1" s="4" t="s">
-        <v>310</v>
       </c>
       <c r="R1" s="4" t="s">
         <v>13</v>
       </c>
       <c r="S1" s="4" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="T1" s="4" t="s">
         <v>14</v>
@@ -1738,34 +1751,34 @@
         <v>294</v>
       </c>
       <c r="X1" s="9" t="s">
+        <v>330</v>
+      </c>
+      <c r="Y1" s="9" t="s">
+        <v>331</v>
+      </c>
+      <c r="Z1" s="9" t="s">
         <v>332</v>
       </c>
-      <c r="Y1" s="9" t="s">
+      <c r="AA1" s="9" t="s">
         <v>333</v>
       </c>
-      <c r="Z1" s="9" t="s">
+      <c r="AB1" s="9" t="s">
         <v>334</v>
       </c>
-      <c r="AA1" s="9" t="s">
-        <v>335</v>
-      </c>
-      <c r="AB1" s="9" t="s">
-        <v>336</v>
-      </c>
       <c r="AC1" s="11" t="s">
+        <v>367</v>
+      </c>
+      <c r="AD1" s="11" t="s">
+        <v>368</v>
+      </c>
+      <c r="AE1" s="11" t="s">
         <v>369</v>
       </c>
-      <c r="AD1" s="11" t="s">
+      <c r="AF1" s="11" t="s">
         <v>370</v>
       </c>
-      <c r="AE1" s="11" t="s">
+      <c r="AG1" s="11" t="s">
         <v>371</v>
-      </c>
-      <c r="AF1" s="11" t="s">
-        <v>372</v>
-      </c>
-      <c r="AG1" s="11" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="2" spans="1:33" s="5" customFormat="1" x14ac:dyDescent="0.35">
@@ -1773,7 +1786,7 @@
         <v>15</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>16</v>
@@ -1816,7 +1829,7 @@
         <v>15</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>16</v>
@@ -1859,7 +1872,7 @@
         <v>15</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>16</v>
@@ -1902,7 +1915,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>16</v>
@@ -2461,7 +2474,7 @@
         <v>24</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>16</v>
@@ -2504,7 +2517,7 @@
         <v>24</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>16</v>
@@ -2547,7 +2560,7 @@
         <v>24</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>16</v>
@@ -2590,7 +2603,7 @@
         <v>24</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>16</v>
@@ -2805,7 +2818,7 @@
         <v>32</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>16</v>
@@ -2848,7 +2861,7 @@
         <v>32</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C27" s="5" t="s">
         <v>16</v>
@@ -2891,7 +2904,7 @@
         <v>32</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C28" s="5" t="s">
         <v>16</v>
@@ -2934,7 +2947,7 @@
         <v>32</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C29" s="5" t="s">
         <v>16</v>
@@ -2977,7 +2990,7 @@
         <v>32</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>16</v>
@@ -3020,7 +3033,7 @@
         <v>32</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C31" s="5" t="s">
         <v>16</v>
@@ -3063,7 +3076,7 @@
         <v>32</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C32" s="5" t="s">
         <v>16</v>
@@ -3106,7 +3119,7 @@
         <v>32</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C33" s="5" t="s">
         <v>16</v>
@@ -3149,7 +3162,7 @@
         <v>32</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C34" s="5" t="s">
         <v>16</v>
@@ -3158,10 +3171,10 @@
         <v>17</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="G34" s="5">
         <v>1</v>
@@ -3192,7 +3205,7 @@
         <v>32</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C35" s="5" t="s">
         <v>16</v>
@@ -3201,10 +3214,10 @@
         <v>17</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="G35" s="5">
         <v>2</v>
@@ -3235,7 +3248,7 @@
         <v>32</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C36" s="5" t="s">
         <v>16</v>
@@ -3244,10 +3257,10 @@
         <v>17</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="G36" s="5">
         <v>3</v>
@@ -3278,7 +3291,7 @@
         <v>32</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C37" s="5" t="s">
         <v>16</v>
@@ -3287,10 +3300,10 @@
         <v>17</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="G37" s="5">
         <v>4</v>
@@ -3321,7 +3334,7 @@
         <v>32</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C38" s="5" t="s">
         <v>16</v>
@@ -3364,7 +3377,7 @@
         <v>32</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C39" s="5" t="s">
         <v>16</v>
@@ -3407,7 +3420,7 @@
         <v>32</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C40" s="5" t="s">
         <v>16</v>
@@ -3450,7 +3463,7 @@
         <v>32</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C41" s="5" t="s">
         <v>16</v>
@@ -3493,7 +3506,7 @@
         <v>32</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C42" s="5" t="s">
         <v>34</v>
@@ -3536,7 +3549,7 @@
         <v>32</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C43" s="5" t="s">
         <v>34</v>
@@ -3574,1449 +3587,1449 @@
       <c r="AA43" s="4"/>
       <c r="AB43" s="4"/>
     </row>
-    <row r="44" spans="1:28" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="12" t="s">
+    <row r="44" spans="1:28" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B44" s="12" t="s">
-        <v>322</v>
-      </c>
-      <c r="C44" s="12" t="s">
+      <c r="B44" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="C44" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="D44" s="12" t="s">
+      <c r="D44" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E44" s="12" t="s">
+      <c r="E44" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="F44" s="12" t="s">
+      <c r="F44" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="G44" s="12">
+      <c r="G44" s="5">
         <v>3</v>
       </c>
-      <c r="H44" s="12">
+      <c r="H44" s="5">
         <v>0.14330000000000001</v>
       </c>
-      <c r="I44" s="12" t="s">
+      <c r="I44" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="J44" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="K44" s="12" t="s">
+      <c r="J44" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K44" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="R44" s="12" t="s">
+      <c r="R44" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="X44" s="13"/>
-      <c r="Y44" s="13"/>
-      <c r="Z44" s="13"/>
-      <c r="AA44" s="13"/>
-      <c r="AB44" s="13"/>
-    </row>
-    <row r="45" spans="1:28" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="12" t="s">
+      <c r="X44" s="4"/>
+      <c r="Y44" s="4"/>
+      <c r="Z44" s="4"/>
+      <c r="AA44" s="4"/>
+      <c r="AB44" s="4"/>
+    </row>
+    <row r="45" spans="1:28" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B45" s="12" t="s">
-        <v>322</v>
-      </c>
-      <c r="C45" s="12" t="s">
+      <c r="B45" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="C45" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="D45" s="12" t="s">
+      <c r="D45" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="E45" s="12" t="s">
+      <c r="E45" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="F45" s="12" t="s">
+      <c r="F45" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="G45" s="12">
+      <c r="G45" s="5">
         <v>4</v>
       </c>
-      <c r="H45" s="12">
+      <c r="H45" s="5">
         <v>0.20300000000000001</v>
       </c>
-      <c r="I45" s="12" t="s">
+      <c r="I45" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="J45" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="K45" s="12" t="s">
+      <c r="J45" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K45" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="R45" s="12" t="s">
+      <c r="R45" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="X45" s="13"/>
-      <c r="Y45" s="13"/>
-      <c r="Z45" s="13"/>
-      <c r="AA45" s="13"/>
-      <c r="AB45" s="13"/>
-    </row>
-    <row r="46" spans="1:28" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="12" t="s">
+      <c r="X45" s="4"/>
+      <c r="Y45" s="4"/>
+      <c r="Z45" s="4"/>
+      <c r="AA45" s="4"/>
+      <c r="AB45" s="4"/>
+    </row>
+    <row r="46" spans="1:28" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B46" s="12" t="s">
+      <c r="B46" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="C46" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="E46" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F46" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G46" s="5">
+        <v>1</v>
+      </c>
+      <c r="H46" s="5">
+        <v>0.14419999999999999</v>
+      </c>
+      <c r="I46" s="5">
+        <v>8.7486999999999995E-2</v>
+      </c>
+      <c r="J46" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K46" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="P46" s="5">
+        <v>1.23</v>
+      </c>
+      <c r="R46" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="T46" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="X46" s="4"/>
+      <c r="Y46" s="4"/>
+      <c r="Z46" s="4"/>
+      <c r="AA46" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="AB46" s="4"/>
+    </row>
+    <row r="47" spans="1:28" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="E47" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F47" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G47" s="5">
+        <v>2</v>
+      </c>
+      <c r="H47" s="5">
+        <v>0.23899999999999999</v>
+      </c>
+      <c r="I47" s="5">
+        <v>8.7297E-2</v>
+      </c>
+      <c r="J47" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K47" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="P47" s="5">
+        <v>1.23</v>
+      </c>
+      <c r="R47" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="T47" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="X47" s="4"/>
+      <c r="Y47" s="4"/>
+      <c r="Z47" s="4"/>
+      <c r="AA47" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="AB47" s="4"/>
+    </row>
+    <row r="48" spans="1:28" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="E48" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F48" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G48" s="5">
+        <v>3</v>
+      </c>
+      <c r="H48" s="5">
+        <v>0.37330000000000002</v>
+      </c>
+      <c r="I48" s="5">
+        <v>8.4613999999999995E-2</v>
+      </c>
+      <c r="J48" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K48" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="P48" s="5">
+        <v>1.23</v>
+      </c>
+      <c r="R48" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="T48" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="X48" s="4"/>
+      <c r="Y48" s="4"/>
+      <c r="Z48" s="4"/>
+      <c r="AA48" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="AB48" s="4"/>
+    </row>
+    <row r="49" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A49" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>313</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="E49" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F49" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G49" s="5">
+        <v>4</v>
+      </c>
+      <c r="H49" s="5">
+        <v>0.69</v>
+      </c>
+      <c r="I49" s="5">
+        <v>8.3804000000000003E-2</v>
+      </c>
+      <c r="J49" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K49" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="P49" s="5">
+        <v>1.23</v>
+      </c>
+      <c r="R49" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="T49" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="X49" s="4"/>
+      <c r="Y49" s="4"/>
+      <c r="Z49" s="4"/>
+      <c r="AA49" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="AB49" s="4"/>
+    </row>
+    <row r="50" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>328</v>
+      </c>
+      <c r="C50" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="E50" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F50" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G50" s="5">
+        <v>1</v>
+      </c>
+      <c r="H50" s="5">
+        <v>0.18001200000000001</v>
+      </c>
+      <c r="I50" s="5">
+        <v>0.116088</v>
+      </c>
+      <c r="J50" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K50" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="L50" s="5">
+        <v>3.69</v>
+      </c>
+      <c r="N50" s="5">
+        <v>10</v>
+      </c>
+      <c r="P50" s="5">
+        <v>1.23</v>
+      </c>
+      <c r="R50" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="T50" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="X50" s="4"/>
+      <c r="Y50" s="4"/>
+      <c r="Z50" s="4"/>
+      <c r="AA50" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="AB50" s="4"/>
+    </row>
+    <row r="51" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A51" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>328</v>
+      </c>
+      <c r="C51" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D51" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="E51" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F51" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G51" s="5">
+        <v>2</v>
+      </c>
+      <c r="H51" s="5">
+        <v>0.25552799999999998</v>
+      </c>
+      <c r="I51" s="5">
+        <v>0.11239200000000001</v>
+      </c>
+      <c r="J51" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K51" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="L51" s="5">
+        <v>3.69</v>
+      </c>
+      <c r="N51" s="5">
+        <v>10</v>
+      </c>
+      <c r="P51" s="5">
+        <v>1.23</v>
+      </c>
+      <c r="R51" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="T51" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="X51" s="4"/>
+      <c r="Y51" s="4"/>
+      <c r="Z51" s="4"/>
+      <c r="AA51" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="AB51" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="AC51" s="7" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="52" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>328</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D52" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="E52" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F52" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G52" s="5">
+        <v>3</v>
+      </c>
+      <c r="H52" s="5">
+        <v>0.41445599999999999</v>
+      </c>
+      <c r="I52" s="5">
+        <v>0.10466399999999999</v>
+      </c>
+      <c r="J52" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K52" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="L52" s="5">
+        <v>3.69</v>
+      </c>
+      <c r="N52" s="5">
+        <v>10</v>
+      </c>
+      <c r="P52" s="5">
+        <v>1.23</v>
+      </c>
+      <c r="R52" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="T52" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="X52" s="4"/>
+      <c r="Y52" s="4"/>
+      <c r="Z52" s="4"/>
+      <c r="AA52" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="AB52" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="AC52" s="7" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="53" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>328</v>
+      </c>
+      <c r="C53" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="E53" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F53" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G53" s="5">
+        <v>4</v>
+      </c>
+      <c r="H53" s="5">
+        <v>0.67325999999999997</v>
+      </c>
+      <c r="I53" s="5">
+        <v>0.103908</v>
+      </c>
+      <c r="J53" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K53" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="L53" s="5">
+        <v>3.69</v>
+      </c>
+      <c r="N53" s="5">
+        <v>10</v>
+      </c>
+      <c r="P53" s="5">
+        <v>1.23</v>
+      </c>
+      <c r="R53" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="T53" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="X53" s="4"/>
+      <c r="Y53" s="4"/>
+      <c r="Z53" s="4"/>
+      <c r="AA53" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="AB53" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="AC53" s="7" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="54" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>327</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D54" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="E54" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F54" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G54" s="5">
+        <v>1</v>
+      </c>
+      <c r="H54" s="5">
+        <v>0.18215500000000001</v>
+      </c>
+      <c r="I54" s="5">
+        <v>0.11747</v>
+      </c>
+      <c r="J54" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K54" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="L54" s="5">
+        <v>3.69</v>
+      </c>
+      <c r="N54" s="5">
+        <v>10</v>
+      </c>
+      <c r="P54" s="5">
+        <v>1.23</v>
+      </c>
+      <c r="R54" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="T54" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="X54" s="4"/>
+      <c r="Y54" s="4"/>
+      <c r="Z54" s="4"/>
+      <c r="AA54" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="AB54" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="AC54" s="7" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="55" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>327</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="E55" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F55" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G55" s="5">
+        <v>2</v>
+      </c>
+      <c r="H55" s="5">
+        <v>0.25857000000000002</v>
+      </c>
+      <c r="I55" s="5">
+        <v>0.11373</v>
+      </c>
+      <c r="J55" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K55" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="L55" s="5">
+        <v>3.69</v>
+      </c>
+      <c r="N55" s="5">
+        <v>10</v>
+      </c>
+      <c r="P55" s="5">
+        <v>1.23</v>
+      </c>
+      <c r="R55" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="T55" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="X55" s="4"/>
+      <c r="Y55" s="4"/>
+      <c r="Z55" s="4"/>
+      <c r="AA55" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="AB55" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="AC55" s="7" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="56" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A56" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>327</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D56" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="E56" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F56" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G56" s="5">
+        <v>3</v>
+      </c>
+      <c r="H56" s="5">
+        <v>0.41938999999999999</v>
+      </c>
+      <c r="I56" s="5">
+        <v>0.10591</v>
+      </c>
+      <c r="J56" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K56" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="L56" s="5">
+        <v>3.69</v>
+      </c>
+      <c r="N56" s="5">
+        <v>10</v>
+      </c>
+      <c r="P56" s="5">
+        <v>1.23</v>
+      </c>
+      <c r="R56" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="T56" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="X56" s="4"/>
+      <c r="Y56" s="4"/>
+      <c r="Z56" s="4"/>
+      <c r="AA56" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="AB56" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="AC56" s="7" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="57" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A57" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>327</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D57" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="E57" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F57" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G57" s="5">
+        <v>4</v>
+      </c>
+      <c r="H57" s="5">
+        <v>0.68127499999999996</v>
+      </c>
+      <c r="I57" s="5">
+        <v>0.105145</v>
+      </c>
+      <c r="J57" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K57" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="L57" s="5">
+        <v>3.69</v>
+      </c>
+      <c r="N57" s="5">
+        <v>10</v>
+      </c>
+      <c r="P57" s="5">
+        <v>1.23</v>
+      </c>
+      <c r="R57" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="T57" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="X57" s="4"/>
+      <c r="Y57" s="4"/>
+      <c r="Z57" s="4"/>
+      <c r="AA57" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="AB57" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="AC57" s="7" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="58" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A58" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D58" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="E58" s="5" t="s">
+        <v>348</v>
+      </c>
+      <c r="F58" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="G58" s="5">
+        <v>1</v>
+      </c>
+      <c r="H58" s="5">
+        <v>0.18429799999999999</v>
+      </c>
+      <c r="I58" s="5">
+        <v>0.118852</v>
+      </c>
+      <c r="J58" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K58" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="L58" s="5">
+        <v>3.69</v>
+      </c>
+      <c r="N58" s="5">
+        <v>10</v>
+      </c>
+      <c r="P58" s="5">
+        <v>1.23</v>
+      </c>
+      <c r="R58" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="T58" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="X58" s="4"/>
+      <c r="Y58" s="4"/>
+      <c r="Z58" s="4"/>
+      <c r="AA58" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="AB58" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="AC58" s="7" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="59" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A59" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="C59" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D59" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="E59" s="5" t="s">
+        <v>348</v>
+      </c>
+      <c r="F59" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="G59" s="5">
+        <v>2</v>
+      </c>
+      <c r="H59" s="5">
+        <v>0.26161200000000001</v>
+      </c>
+      <c r="I59" s="5">
+        <v>0.115068</v>
+      </c>
+      <c r="J59" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K59" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="L59" s="5">
+        <v>3.69</v>
+      </c>
+      <c r="N59" s="5">
+        <v>10</v>
+      </c>
+      <c r="P59" s="5">
+        <v>1.23</v>
+      </c>
+      <c r="R59" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="T59" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="X59" s="4"/>
+      <c r="Y59" s="4"/>
+      <c r="Z59" s="4"/>
+      <c r="AA59" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="AB59" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="AC59" s="7" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="60" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A60" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="C60" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D60" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="E60" s="5" t="s">
+        <v>348</v>
+      </c>
+      <c r="F60" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="G60" s="5">
+        <v>3</v>
+      </c>
+      <c r="H60" s="5">
+        <v>0.42432399999999998</v>
+      </c>
+      <c r="I60" s="5">
+        <v>0.107156</v>
+      </c>
+      <c r="J60" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K60" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="L60" s="5">
+        <v>3.69</v>
+      </c>
+      <c r="N60" s="5">
+        <v>10</v>
+      </c>
+      <c r="P60" s="5">
+        <v>1.23</v>
+      </c>
+      <c r="R60" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="T60" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="X60" s="4"/>
+      <c r="Y60" s="4"/>
+      <c r="Z60" s="4"/>
+      <c r="AA60" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="AB60" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="AC60" s="7" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="61" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A61" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="C61" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D61" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="E61" s="5" t="s">
+        <v>348</v>
+      </c>
+      <c r="F61" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="G61" s="5">
+        <v>4</v>
+      </c>
+      <c r="H61" s="5">
+        <v>0.68928999999999996</v>
+      </c>
+      <c r="I61" s="5">
+        <v>0.106382</v>
+      </c>
+      <c r="J61" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K61" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="L61" s="5">
+        <v>3.69</v>
+      </c>
+      <c r="N61" s="5">
+        <v>10</v>
+      </c>
+      <c r="P61" s="5">
+        <v>1.23</v>
+      </c>
+      <c r="R61" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="T61" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="X61" s="4"/>
+      <c r="Y61" s="4"/>
+      <c r="Z61" s="4"/>
+      <c r="AA61" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="AB61" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="AC61" s="7" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="62" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A62" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="C62" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D62" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="E62" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F62" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G62" s="5">
+        <v>1</v>
+      </c>
+      <c r="H62" s="5">
+        <v>0.1288</v>
+      </c>
+      <c r="I62" s="5">
+        <v>8.8959999999999997E-2</v>
+      </c>
+      <c r="J62" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K62" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="P62" s="5">
+        <v>1.23</v>
+      </c>
+      <c r="R62" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="T62" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="X62" s="4"/>
+      <c r="Y62" s="4"/>
+      <c r="Z62" s="4"/>
+      <c r="AA62" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="AB62" s="4"/>
+    </row>
+    <row r="63" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A63" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="C63" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D63" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="E63" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F63" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G63" s="5">
+        <v>2</v>
+      </c>
+      <c r="H63" s="5">
+        <v>0.23896000000000001</v>
+      </c>
+      <c r="I63" s="5">
+        <v>8.5279999999999995E-2</v>
+      </c>
+      <c r="J63" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K63" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="P63" s="5">
+        <v>1.23</v>
+      </c>
+      <c r="R63" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="T63" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="X63" s="4"/>
+      <c r="Y63" s="4"/>
+      <c r="Z63" s="4"/>
+      <c r="AA63" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="AB63" s="4"/>
+    </row>
+    <row r="64" spans="1:29" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A64" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="C64" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D64" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="E64" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F64" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G64" s="5">
+        <v>1</v>
+      </c>
+      <c r="H64" s="5">
+        <v>0.15165300000000001</v>
+      </c>
+      <c r="I64" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="J64" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K64" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="P64" s="5">
+        <v>1.23</v>
+      </c>
+      <c r="R64" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="T64" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="X64" s="4"/>
+      <c r="Y64" s="4"/>
+      <c r="Z64" s="4"/>
+      <c r="AA64" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="AB64" s="4"/>
+    </row>
+    <row r="65" spans="1:28" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A65" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="C65" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D65" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="E65" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F65" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G65" s="5">
+        <v>2</v>
+      </c>
+      <c r="H65" s="5">
+        <v>0.187253</v>
+      </c>
+      <c r="I65" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="J65" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K65" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="P65" s="5">
+        <v>1.23</v>
+      </c>
+      <c r="R65" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="T65" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="X65" s="4"/>
+      <c r="Y65" s="4"/>
+      <c r="Z65" s="4"/>
+      <c r="AA65" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="AB65" s="4"/>
+    </row>
+    <row r="66" spans="1:28" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A66" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="C66" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D66" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="E66" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F66" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G66" s="5">
+        <v>3</v>
+      </c>
+      <c r="H66" s="5">
+        <v>0.22175300000000001</v>
+      </c>
+      <c r="I66" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="J66" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K66" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="P66" s="5">
+        <v>1.23</v>
+      </c>
+      <c r="R66" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="T66" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="X66" s="4"/>
+      <c r="Y66" s="4"/>
+      <c r="Z66" s="4"/>
+      <c r="AA66" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="AB66" s="4"/>
+    </row>
+    <row r="67" spans="1:28" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A67" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="C67" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D67" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="E67" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F67" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G67" s="5">
+        <v>4</v>
+      </c>
+      <c r="H67" s="5">
+        <v>0.28145300000000001</v>
+      </c>
+      <c r="I67" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="J67" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K67" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="P67" s="5">
+        <v>1.23</v>
+      </c>
+      <c r="R67" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="T67" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="X67" s="4"/>
+      <c r="Y67" s="4"/>
+      <c r="Z67" s="4"/>
+      <c r="AA67" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="AB67" s="4"/>
+    </row>
+    <row r="68" spans="1:28" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A68" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B68" s="5" t="s">
         <v>315</v>
       </c>
-      <c r="C46" s="12" t="s">
+      <c r="C68" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D46" s="12" t="s">
+      <c r="D68" s="5" t="s">
         <v>299</v>
       </c>
-      <c r="E46" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="F46" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="G46" s="12">
+      <c r="E68" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F68" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G68" s="5">
         <v>1</v>
       </c>
-      <c r="H46" s="12">
-        <v>0.14419999999999999</v>
-      </c>
-      <c r="I46" s="12">
-        <v>8.7486999999999995E-2</v>
-      </c>
-      <c r="J46" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="K46" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="P46" s="12">
+      <c r="H68" s="5">
+        <v>0.1646</v>
+      </c>
+      <c r="I68" s="5">
+        <v>0.100476</v>
+      </c>
+      <c r="J68" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K68" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="P68" s="5">
         <v>1.23</v>
       </c>
-      <c r="R46" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="T46" s="12" t="s">
-        <v>312</v>
-      </c>
-      <c r="X46" s="13"/>
-      <c r="Y46" s="13"/>
-      <c r="Z46" s="13"/>
-      <c r="AA46" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="AB46" s="13"/>
-    </row>
-    <row r="47" spans="1:28" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="12" t="s">
+      <c r="R68" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="T68" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="X68" s="4"/>
+      <c r="Y68" s="4"/>
+      <c r="Z68" s="4"/>
+      <c r="AA68" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="AB68" s="4"/>
+    </row>
+    <row r="69" spans="1:28" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A69" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B47" s="12" t="s">
+      <c r="B69" s="5" t="s">
         <v>315</v>
       </c>
-      <c r="C47" s="12" t="s">
+      <c r="C69" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D47" s="12" t="s">
+      <c r="D69" s="5" t="s">
         <v>299</v>
       </c>
-      <c r="E47" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="F47" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="G47" s="12">
+      <c r="E69" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F69" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G69" s="5">
         <v>2</v>
       </c>
-      <c r="H47" s="12">
-        <v>0.23899999999999999</v>
-      </c>
-      <c r="I47" s="12">
-        <v>8.7297E-2</v>
-      </c>
-      <c r="J47" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="K47" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="P47" s="12">
+      <c r="H69" s="5">
+        <v>0.28120000000000001</v>
+      </c>
+      <c r="I69" s="5">
+        <v>9.9721000000000004E-2</v>
+      </c>
+      <c r="J69" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K69" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="P69" s="5">
         <v>1.23</v>
       </c>
-      <c r="R47" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="T47" s="12" t="s">
-        <v>312</v>
-      </c>
-      <c r="X47" s="13"/>
-      <c r="Y47" s="13"/>
-      <c r="Z47" s="13"/>
-      <c r="AA47" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="AB47" s="13"/>
-    </row>
-    <row r="48" spans="1:28" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="B48" s="12" t="s">
-        <v>315</v>
-      </c>
-      <c r="C48" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="D48" s="12" t="s">
-        <v>299</v>
-      </c>
-      <c r="E48" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="F48" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="G48" s="12">
-        <v>3</v>
-      </c>
-      <c r="H48" s="12">
-        <v>0.37330000000000002</v>
-      </c>
-      <c r="I48" s="12">
-        <v>8.4613999999999995E-2</v>
-      </c>
-      <c r="J48" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="K48" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="P48" s="12">
-        <v>1.23</v>
-      </c>
-      <c r="R48" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="T48" s="12" t="s">
-        <v>312</v>
-      </c>
-      <c r="X48" s="13"/>
-      <c r="Y48" s="13"/>
-      <c r="Z48" s="13"/>
-      <c r="AA48" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="AB48" s="13"/>
-    </row>
-    <row r="49" spans="1:29" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="B49" s="12" t="s">
-        <v>315</v>
-      </c>
-      <c r="C49" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="D49" s="12" t="s">
-        <v>299</v>
-      </c>
-      <c r="E49" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="F49" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="G49" s="12">
-        <v>4</v>
-      </c>
-      <c r="H49" s="12">
-        <v>0.69</v>
-      </c>
-      <c r="I49" s="12">
-        <v>8.3804000000000003E-2</v>
-      </c>
-      <c r="J49" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="K49" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="P49" s="12">
-        <v>1.23</v>
-      </c>
-      <c r="R49" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="T49" s="12" t="s">
-        <v>312</v>
-      </c>
-      <c r="X49" s="13"/>
-      <c r="Y49" s="13"/>
-      <c r="Z49" s="13"/>
-      <c r="AA49" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="AB49" s="13"/>
-    </row>
-    <row r="50" spans="1:29" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="B50" s="12" t="s">
-        <v>330</v>
-      </c>
-      <c r="C50" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="D50" s="12" t="s">
-        <v>299</v>
-      </c>
-      <c r="E50" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="F50" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="G50" s="12">
-        <v>1</v>
-      </c>
-      <c r="H50" s="12">
-        <v>0.18001200000000001</v>
-      </c>
-      <c r="I50" s="12">
-        <v>0.116088</v>
-      </c>
-      <c r="J50" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="K50" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="L50" s="12">
-        <v>3.69</v>
-      </c>
-      <c r="N50" s="12">
-        <v>10</v>
-      </c>
-      <c r="P50" s="12">
-        <v>1.23</v>
-      </c>
-      <c r="R50" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="T50" s="12" t="s">
-        <v>331</v>
-      </c>
-      <c r="X50" s="13"/>
-      <c r="Y50" s="13"/>
-      <c r="Z50" s="13"/>
-      <c r="AA50" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="AB50" s="13"/>
-    </row>
-    <row r="51" spans="1:29" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="B51" s="12" t="s">
-        <v>330</v>
-      </c>
-      <c r="C51" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="D51" s="12" t="s">
-        <v>299</v>
-      </c>
-      <c r="E51" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="F51" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="G51" s="12">
-        <v>2</v>
-      </c>
-      <c r="H51" s="12">
-        <v>0.25552799999999998</v>
-      </c>
-      <c r="I51" s="12">
-        <v>0.11239200000000001</v>
-      </c>
-      <c r="J51" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="K51" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="L51" s="12">
-        <v>3.69</v>
-      </c>
-      <c r="N51" s="12">
-        <v>10</v>
-      </c>
-      <c r="P51" s="12">
-        <v>1.23</v>
-      </c>
-      <c r="R51" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="T51" s="12" t="s">
-        <v>331</v>
-      </c>
-      <c r="X51" s="13"/>
-      <c r="Y51" s="13"/>
-      <c r="Z51" s="13"/>
-      <c r="AA51" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="AB51" s="14" t="s">
-        <v>374</v>
-      </c>
-      <c r="AC51" s="14" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="52" spans="1:29" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="B52" s="12" t="s">
-        <v>330</v>
-      </c>
-      <c r="C52" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="D52" s="12" t="s">
-        <v>299</v>
-      </c>
-      <c r="E52" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="F52" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="G52" s="12">
-        <v>3</v>
-      </c>
-      <c r="H52" s="12">
-        <v>0.41445599999999999</v>
-      </c>
-      <c r="I52" s="12">
-        <v>0.10466399999999999</v>
-      </c>
-      <c r="J52" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="K52" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="L52" s="12">
-        <v>3.69</v>
-      </c>
-      <c r="N52" s="12">
-        <v>10</v>
-      </c>
-      <c r="P52" s="12">
-        <v>1.23</v>
-      </c>
-      <c r="R52" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="T52" s="12" t="s">
-        <v>331</v>
-      </c>
-      <c r="X52" s="13"/>
-      <c r="Y52" s="13"/>
-      <c r="Z52" s="13"/>
-      <c r="AA52" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="AB52" s="14" t="s">
-        <v>374</v>
-      </c>
-      <c r="AC52" s="14" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="53" spans="1:29" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="B53" s="12" t="s">
-        <v>330</v>
-      </c>
-      <c r="C53" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="D53" s="12" t="s">
-        <v>299</v>
-      </c>
-      <c r="E53" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="F53" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="G53" s="12">
-        <v>4</v>
-      </c>
-      <c r="H53" s="12">
-        <v>0.67325999999999997</v>
-      </c>
-      <c r="I53" s="12">
-        <v>0.103908</v>
-      </c>
-      <c r="J53" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="K53" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="L53" s="12">
-        <v>3.69</v>
-      </c>
-      <c r="N53" s="12">
-        <v>10</v>
-      </c>
-      <c r="P53" s="12">
-        <v>1.23</v>
-      </c>
-      <c r="R53" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="T53" s="12" t="s">
-        <v>331</v>
-      </c>
-      <c r="X53" s="13"/>
-      <c r="Y53" s="13"/>
-      <c r="Z53" s="13"/>
-      <c r="AA53" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="AB53" s="14" t="s">
-        <v>374</v>
-      </c>
-      <c r="AC53" s="14" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="54" spans="1:29" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="B54" s="12" t="s">
-        <v>329</v>
-      </c>
-      <c r="C54" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="D54" s="12" t="s">
-        <v>299</v>
-      </c>
-      <c r="E54" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="F54" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="G54" s="12">
-        <v>1</v>
-      </c>
-      <c r="H54" s="12">
-        <v>0.18215500000000001</v>
-      </c>
-      <c r="I54" s="12">
-        <v>0.11747</v>
-      </c>
-      <c r="J54" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="K54" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="L54" s="12">
-        <v>3.69</v>
-      </c>
-      <c r="N54" s="12">
-        <v>10</v>
-      </c>
-      <c r="P54" s="12">
-        <v>1.23</v>
-      </c>
-      <c r="R54" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="T54" s="12" t="s">
-        <v>331</v>
-      </c>
-      <c r="X54" s="13"/>
-      <c r="Y54" s="13"/>
-      <c r="Z54" s="13"/>
-      <c r="AA54" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="AB54" s="14" t="s">
-        <v>374</v>
-      </c>
-      <c r="AC54" s="14" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="55" spans="1:29" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="B55" s="12" t="s">
-        <v>329</v>
-      </c>
-      <c r="C55" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="D55" s="12" t="s">
-        <v>299</v>
-      </c>
-      <c r="E55" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="F55" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="G55" s="12">
-        <v>2</v>
-      </c>
-      <c r="H55" s="12">
-        <v>0.25857000000000002</v>
-      </c>
-      <c r="I55" s="12">
-        <v>0.11373</v>
-      </c>
-      <c r="J55" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="K55" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="L55" s="12">
-        <v>3.69</v>
-      </c>
-      <c r="N55" s="12">
-        <v>10</v>
-      </c>
-      <c r="P55" s="12">
-        <v>1.23</v>
-      </c>
-      <c r="R55" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="T55" s="12" t="s">
-        <v>331</v>
-      </c>
-      <c r="X55" s="13"/>
-      <c r="Y55" s="13"/>
-      <c r="Z55" s="13"/>
-      <c r="AA55" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="AB55" s="14" t="s">
-        <v>374</v>
-      </c>
-      <c r="AC55" s="14" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="56" spans="1:29" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="B56" s="12" t="s">
-        <v>329</v>
-      </c>
-      <c r="C56" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="D56" s="12" t="s">
-        <v>299</v>
-      </c>
-      <c r="E56" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="F56" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="G56" s="12">
-        <v>3</v>
-      </c>
-      <c r="H56" s="12">
-        <v>0.41938999999999999</v>
-      </c>
-      <c r="I56" s="12">
-        <v>0.10591</v>
-      </c>
-      <c r="J56" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="K56" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="L56" s="12">
-        <v>3.69</v>
-      </c>
-      <c r="N56" s="12">
-        <v>10</v>
-      </c>
-      <c r="P56" s="12">
-        <v>1.23</v>
-      </c>
-      <c r="R56" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="T56" s="12" t="s">
-        <v>331</v>
-      </c>
-      <c r="X56" s="13"/>
-      <c r="Y56" s="13"/>
-      <c r="Z56" s="13"/>
-      <c r="AA56" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="AB56" s="14" t="s">
-        <v>374</v>
-      </c>
-      <c r="AC56" s="14" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="57" spans="1:29" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="B57" s="12" t="s">
-        <v>329</v>
-      </c>
-      <c r="C57" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="D57" s="12" t="s">
-        <v>299</v>
-      </c>
-      <c r="E57" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="F57" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="G57" s="12">
-        <v>4</v>
-      </c>
-      <c r="H57" s="12">
-        <v>0.68127499999999996</v>
-      </c>
-      <c r="I57" s="12">
-        <v>0.105145</v>
-      </c>
-      <c r="J57" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="K57" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="L57" s="12">
-        <v>3.69</v>
-      </c>
-      <c r="N57" s="12">
-        <v>10</v>
-      </c>
-      <c r="P57" s="12">
-        <v>1.23</v>
-      </c>
-      <c r="R57" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="T57" s="12" t="s">
-        <v>331</v>
-      </c>
-      <c r="X57" s="13"/>
-      <c r="Y57" s="13"/>
-      <c r="Z57" s="13"/>
-      <c r="AA57" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="AB57" s="14" t="s">
-        <v>374</v>
-      </c>
-      <c r="AC57" s="14" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="58" spans="1:29" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="B58" s="12" t="s">
-        <v>348</v>
-      </c>
-      <c r="C58" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="D58" s="12" t="s">
-        <v>299</v>
-      </c>
-      <c r="E58" s="12" t="s">
-        <v>350</v>
-      </c>
-      <c r="F58" s="12" t="s">
-        <v>344</v>
-      </c>
-      <c r="G58" s="12">
-        <v>1</v>
-      </c>
-      <c r="H58" s="12">
-        <v>0.18429799999999999</v>
-      </c>
-      <c r="I58" s="12">
-        <v>0.118852</v>
-      </c>
-      <c r="J58" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="K58" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="L58" s="12">
-        <v>3.69</v>
-      </c>
-      <c r="N58" s="12">
-        <v>10</v>
-      </c>
-      <c r="P58" s="12">
-        <v>1.23</v>
-      </c>
-      <c r="R58" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="T58" s="12" t="s">
-        <v>331</v>
-      </c>
-      <c r="X58" s="13"/>
-      <c r="Y58" s="13"/>
-      <c r="Z58" s="13"/>
-      <c r="AA58" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="AB58" s="14" t="s">
-        <v>374</v>
-      </c>
-      <c r="AC58" s="14" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="59" spans="1:29" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A59" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="B59" s="12" t="s">
-        <v>348</v>
-      </c>
-      <c r="C59" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="D59" s="12" t="s">
-        <v>299</v>
-      </c>
-      <c r="E59" s="12" t="s">
-        <v>350</v>
-      </c>
-      <c r="F59" s="12" t="s">
-        <v>344</v>
-      </c>
-      <c r="G59" s="12">
-        <v>2</v>
-      </c>
-      <c r="H59" s="12">
-        <v>0.26161200000000001</v>
-      </c>
-      <c r="I59" s="12">
-        <v>0.115068</v>
-      </c>
-      <c r="J59" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="K59" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="L59" s="12">
-        <v>3.69</v>
-      </c>
-      <c r="N59" s="12">
-        <v>10</v>
-      </c>
-      <c r="P59" s="12">
-        <v>1.23</v>
-      </c>
-      <c r="R59" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="T59" s="12" t="s">
-        <v>331</v>
-      </c>
-      <c r="X59" s="13"/>
-      <c r="Y59" s="13"/>
-      <c r="Z59" s="13"/>
-      <c r="AA59" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="AB59" s="14" t="s">
-        <v>374</v>
-      </c>
-      <c r="AC59" s="14" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="60" spans="1:29" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A60" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="B60" s="12" t="s">
-        <v>348</v>
-      </c>
-      <c r="C60" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="D60" s="12" t="s">
-        <v>299</v>
-      </c>
-      <c r="E60" s="12" t="s">
-        <v>350</v>
-      </c>
-      <c r="F60" s="12" t="s">
-        <v>344</v>
-      </c>
-      <c r="G60" s="12">
-        <v>3</v>
-      </c>
-      <c r="H60" s="12">
-        <v>0.42432399999999998</v>
-      </c>
-      <c r="I60" s="12">
-        <v>0.107156</v>
-      </c>
-      <c r="J60" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="K60" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="L60" s="12">
-        <v>3.69</v>
-      </c>
-      <c r="N60" s="12">
-        <v>10</v>
-      </c>
-      <c r="P60" s="12">
-        <v>1.23</v>
-      </c>
-      <c r="R60" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="T60" s="12" t="s">
-        <v>331</v>
-      </c>
-      <c r="X60" s="13"/>
-      <c r="Y60" s="13"/>
-      <c r="Z60" s="13"/>
-      <c r="AA60" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="AB60" s="14" t="s">
-        <v>374</v>
-      </c>
-      <c r="AC60" s="14" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="61" spans="1:29" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A61" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="B61" s="12" t="s">
-        <v>348</v>
-      </c>
-      <c r="C61" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="D61" s="12" t="s">
-        <v>299</v>
-      </c>
-      <c r="E61" s="12" t="s">
-        <v>350</v>
-      </c>
-      <c r="F61" s="12" t="s">
-        <v>344</v>
-      </c>
-      <c r="G61" s="12">
-        <v>4</v>
-      </c>
-      <c r="H61" s="12">
-        <v>0.68928999999999996</v>
-      </c>
-      <c r="I61" s="12">
-        <v>0.106382</v>
-      </c>
-      <c r="J61" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="K61" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="L61" s="12">
-        <v>3.69</v>
-      </c>
-      <c r="N61" s="12">
-        <v>10</v>
-      </c>
-      <c r="P61" s="12">
-        <v>1.23</v>
-      </c>
-      <c r="R61" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="T61" s="12" t="s">
-        <v>331</v>
-      </c>
-      <c r="X61" s="13"/>
-      <c r="Y61" s="13"/>
-      <c r="Z61" s="13"/>
-      <c r="AA61" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="AB61" s="14" t="s">
-        <v>374</v>
-      </c>
-      <c r="AC61" s="14" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="62" spans="1:29" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A62" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="B62" s="12" t="s">
-        <v>316</v>
-      </c>
-      <c r="C62" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="D62" s="12" t="s">
-        <v>299</v>
-      </c>
-      <c r="E62" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="F62" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="G62" s="12">
-        <v>1</v>
-      </c>
-      <c r="H62" s="12">
-        <v>0.1288</v>
-      </c>
-      <c r="I62" s="12">
-        <v>8.8959999999999997E-2</v>
-      </c>
-      <c r="J62" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="K62" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="P62" s="12">
-        <v>1.23</v>
-      </c>
-      <c r="R62" s="12" t="s">
-        <v>314</v>
-      </c>
-      <c r="T62" s="12" t="s">
-        <v>312</v>
-      </c>
-      <c r="X62" s="13"/>
-      <c r="Y62" s="13"/>
-      <c r="Z62" s="13"/>
-      <c r="AA62" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="AB62" s="13"/>
-    </row>
-    <row r="63" spans="1:29" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="B63" s="12" t="s">
-        <v>316</v>
-      </c>
-      <c r="C63" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="D63" s="12" t="s">
-        <v>299</v>
-      </c>
-      <c r="E63" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="F63" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="G63" s="12">
-        <v>2</v>
-      </c>
-      <c r="H63" s="12">
-        <v>0.23896000000000001</v>
-      </c>
-      <c r="I63" s="12">
-        <v>8.5279999999999995E-2</v>
-      </c>
-      <c r="J63" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="K63" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="P63" s="12">
-        <v>1.23</v>
-      </c>
-      <c r="R63" s="12" t="s">
-        <v>314</v>
-      </c>
-      <c r="T63" s="12" t="s">
-        <v>312</v>
-      </c>
-      <c r="X63" s="13"/>
-      <c r="Y63" s="13"/>
-      <c r="Z63" s="13"/>
-      <c r="AA63" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="AB63" s="13"/>
-    </row>
-    <row r="64" spans="1:29" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="B64" s="12" t="s">
-        <v>319</v>
-      </c>
-      <c r="C64" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="D64" s="12" t="s">
-        <v>299</v>
-      </c>
-      <c r="E64" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="F64" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="G64" s="12">
-        <v>1</v>
-      </c>
-      <c r="H64" s="12">
-        <v>0.15165300000000001</v>
-      </c>
-      <c r="I64" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="J64" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="K64" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="P64" s="12">
-        <v>1.23</v>
-      </c>
-      <c r="R64" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="T64" s="12" t="s">
-        <v>312</v>
-      </c>
-      <c r="X64" s="13"/>
-      <c r="Y64" s="13"/>
-      <c r="Z64" s="13"/>
-      <c r="AA64" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="AB64" s="13"/>
-    </row>
-    <row r="65" spans="1:28" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="B65" s="12" t="s">
-        <v>319</v>
-      </c>
-      <c r="C65" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="D65" s="12" t="s">
-        <v>299</v>
-      </c>
-      <c r="E65" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="F65" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="G65" s="12">
-        <v>2</v>
-      </c>
-      <c r="H65" s="12">
-        <v>0.187253</v>
-      </c>
-      <c r="I65" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="J65" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="K65" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="P65" s="12">
-        <v>1.23</v>
-      </c>
-      <c r="R65" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="T65" s="12" t="s">
-        <v>312</v>
-      </c>
-      <c r="X65" s="13"/>
-      <c r="Y65" s="13"/>
-      <c r="Z65" s="13"/>
-      <c r="AA65" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="AB65" s="13"/>
-    </row>
-    <row r="66" spans="1:28" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="B66" s="12" t="s">
-        <v>319</v>
-      </c>
-      <c r="C66" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="D66" s="12" t="s">
-        <v>299</v>
-      </c>
-      <c r="E66" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="F66" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="G66" s="12">
-        <v>3</v>
-      </c>
-      <c r="H66" s="12">
-        <v>0.22175300000000001</v>
-      </c>
-      <c r="I66" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="J66" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="K66" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="P66" s="12">
-        <v>1.23</v>
-      </c>
-      <c r="R66" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="T66" s="12" t="s">
-        <v>312</v>
-      </c>
-      <c r="X66" s="13"/>
-      <c r="Y66" s="13"/>
-      <c r="Z66" s="13"/>
-      <c r="AA66" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="AB66" s="13"/>
-    </row>
-    <row r="67" spans="1:28" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="B67" s="12" t="s">
-        <v>319</v>
-      </c>
-      <c r="C67" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="D67" s="12" t="s">
-        <v>299</v>
-      </c>
-      <c r="E67" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="F67" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="G67" s="12">
-        <v>4</v>
-      </c>
-      <c r="H67" s="12">
-        <v>0.28145300000000001</v>
-      </c>
-      <c r="I67" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="J67" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="K67" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="P67" s="12">
-        <v>1.23</v>
-      </c>
-      <c r="R67" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="T67" s="12" t="s">
-        <v>312</v>
-      </c>
-      <c r="X67" s="13"/>
-      <c r="Y67" s="13"/>
-      <c r="Z67" s="13"/>
-      <c r="AA67" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="AB67" s="13"/>
-    </row>
-    <row r="68" spans="1:28" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="B68" s="12" t="s">
-        <v>317</v>
-      </c>
-      <c r="C68" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="D68" s="12" t="s">
-        <v>299</v>
-      </c>
-      <c r="E68" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="F68" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="G68" s="12">
-        <v>1</v>
-      </c>
-      <c r="H68" s="12">
-        <v>0.1646</v>
-      </c>
-      <c r="I68" s="12">
-        <v>0.100476</v>
-      </c>
-      <c r="J68" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="K68" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="P68" s="12">
-        <v>1.23</v>
-      </c>
-      <c r="R68" s="12" t="s">
+      <c r="R69" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="T68" s="12" t="s">
-        <v>313</v>
-      </c>
-      <c r="X68" s="13"/>
-      <c r="Y68" s="13"/>
-      <c r="Z68" s="13"/>
-      <c r="AA68" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="AB68" s="13"/>
-    </row>
-    <row r="69" spans="1:28" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="B69" s="12" t="s">
-        <v>317</v>
-      </c>
-      <c r="C69" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="D69" s="12" t="s">
-        <v>299</v>
-      </c>
-      <c r="E69" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="F69" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="G69" s="12">
-        <v>2</v>
-      </c>
-      <c r="H69" s="12">
-        <v>0.28120000000000001</v>
-      </c>
-      <c r="I69" s="12">
-        <v>9.9721000000000004E-2</v>
-      </c>
-      <c r="J69" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="K69" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="P69" s="12">
-        <v>1.23</v>
-      </c>
-      <c r="R69" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="T69" s="12" t="s">
-        <v>313</v>
-      </c>
-      <c r="X69" s="13"/>
-      <c r="Y69" s="13"/>
-      <c r="Z69" s="13"/>
-      <c r="AA69" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="AB69" s="13"/>
+      <c r="T69" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="X69" s="4"/>
+      <c r="Y69" s="4"/>
+      <c r="Z69" s="4"/>
+      <c r="AA69" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="AB69" s="4"/>
     </row>
     <row r="70" spans="1:28" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A70" s="5" t="s">
         <v>38</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C70" s="5" t="s">
         <v>16</v>
@@ -5052,7 +5065,7 @@
         <v>42</v>
       </c>
       <c r="T70" s="5" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="X70" s="4"/>
       <c r="Y70" s="4"/>
@@ -5067,7 +5080,7 @@
         <v>38</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C71" s="5" t="s">
         <v>16</v>
@@ -5103,7 +5116,7 @@
         <v>42</v>
       </c>
       <c r="T71" s="5" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="X71" s="4"/>
       <c r="Y71" s="4"/>
@@ -5118,7 +5131,7 @@
         <v>38</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C72" s="5" t="s">
         <v>16</v>
@@ -5151,7 +5164,7 @@
         <v>39</v>
       </c>
       <c r="T72" s="5" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="X72" s="4"/>
       <c r="Y72" s="4"/>
@@ -5164,7 +5177,7 @@
         <v>38</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C73" s="5" t="s">
         <v>16</v>
@@ -5197,7 +5210,7 @@
         <v>39</v>
       </c>
       <c r="T73" s="5" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="X73" s="4"/>
       <c r="Y73" s="4"/>
@@ -5210,7 +5223,7 @@
         <v>38</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C74" s="5" t="s">
         <v>16</v>
@@ -5243,7 +5256,7 @@
         <v>39</v>
       </c>
       <c r="T74" s="5" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="X74" s="4"/>
       <c r="Y74" s="4"/>
@@ -5256,7 +5269,7 @@
         <v>38</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C75" s="5" t="s">
         <v>16</v>
@@ -5289,7 +5302,7 @@
         <v>39</v>
       </c>
       <c r="T75" s="5" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="X75" s="4"/>
       <c r="Y75" s="4"/>
@@ -5302,7 +5315,7 @@
         <v>38</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C76" s="5" t="s">
         <v>16</v>
@@ -5335,7 +5348,7 @@
         <v>40</v>
       </c>
       <c r="T76" s="5" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="X76" s="4"/>
       <c r="Y76" s="4"/>
@@ -5348,7 +5361,7 @@
         <v>38</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C77" s="5" t="s">
         <v>16</v>
@@ -5381,7 +5394,7 @@
         <v>40</v>
       </c>
       <c r="T77" s="5" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="X77" s="4"/>
       <c r="Y77" s="4"/>
@@ -5394,7 +5407,7 @@
         <v>38</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C78" s="5" t="s">
         <v>16</v>
@@ -5427,7 +5440,7 @@
         <v>40</v>
       </c>
       <c r="T78" s="5" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="X78" s="4"/>
       <c r="Y78" s="4"/>
@@ -5440,7 +5453,7 @@
         <v>38</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C79" s="5" t="s">
         <v>16</v>
@@ -5473,7 +5486,7 @@
         <v>40</v>
       </c>
       <c r="T79" s="5" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="X79" s="4"/>
       <c r="Y79" s="4"/>
@@ -5486,7 +5499,7 @@
         <v>38</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C80" s="5" t="s">
         <v>16</v>
@@ -5519,7 +5532,7 @@
         <v>40</v>
       </c>
       <c r="T80" s="5" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="X80" s="4"/>
       <c r="Y80" s="4"/>
@@ -5532,7 +5545,7 @@
         <v>38</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C81" s="5" t="s">
         <v>16</v>
@@ -5565,7 +5578,7 @@
         <v>40</v>
       </c>
       <c r="T81" s="5" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="X81" s="4"/>
       <c r="Y81" s="4"/>
@@ -5578,7 +5591,7 @@
         <v>38</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C82" s="5" t="s">
         <v>16</v>
@@ -5611,7 +5624,7 @@
         <v>40</v>
       </c>
       <c r="T82" s="5" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="X82" s="4"/>
       <c r="Y82" s="4"/>
@@ -5624,7 +5637,7 @@
         <v>38</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C83" s="5" t="s">
         <v>16</v>
@@ -5657,7 +5670,7 @@
         <v>40</v>
       </c>
       <c r="T83" s="5" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="X83" s="4"/>
       <c r="Y83" s="4"/>
@@ -5670,7 +5683,7 @@
         <v>38</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C84" s="5" t="s">
         <v>16</v>
@@ -5679,10 +5692,10 @@
         <v>299</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="F84" s="5" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="G84" s="5">
         <v>1</v>
@@ -5703,7 +5716,7 @@
         <v>40</v>
       </c>
       <c r="T84" s="5" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="X84" s="4"/>
       <c r="Y84" s="4"/>
@@ -5716,7 +5729,7 @@
         <v>38</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C85" s="5" t="s">
         <v>16</v>
@@ -5725,10 +5738,10 @@
         <v>299</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="F85" s="5" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="G85" s="5">
         <v>2</v>
@@ -5749,7 +5762,7 @@
         <v>40</v>
       </c>
       <c r="T85" s="5" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="X85" s="4"/>
       <c r="Y85" s="4"/>
@@ -5762,7 +5775,7 @@
         <v>38</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C86" s="5" t="s">
         <v>16</v>
@@ -5771,10 +5784,10 @@
         <v>299</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="F86" s="5" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="G86" s="5">
         <v>3</v>
@@ -5795,7 +5808,7 @@
         <v>40</v>
       </c>
       <c r="T86" s="5" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="X86" s="4"/>
       <c r="Y86" s="4"/>
@@ -5808,7 +5821,7 @@
         <v>38</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C87" s="5" t="s">
         <v>16</v>
@@ -5817,10 +5830,10 @@
         <v>299</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="F87" s="5" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="G87" s="5">
         <v>4</v>
@@ -5841,7 +5854,7 @@
         <v>40</v>
       </c>
       <c r="T87" s="5" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="X87" s="4"/>
       <c r="Y87" s="4"/>
@@ -5854,7 +5867,7 @@
         <v>38</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C88" s="5" t="s">
         <v>16</v>
@@ -5884,10 +5897,10 @@
         <v>20</v>
       </c>
       <c r="R88" s="5" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="T88" s="5" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="X88" s="4"/>
       <c r="Y88" s="4"/>
@@ -5900,7 +5913,7 @@
         <v>38</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C89" s="5" t="s">
         <v>16</v>
@@ -5930,10 +5943,10 @@
         <v>20</v>
       </c>
       <c r="R89" s="5" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="T89" s="5" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="X89" s="4"/>
       <c r="Y89" s="4"/>
@@ -5946,7 +5959,7 @@
         <v>38</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C90" s="5" t="s">
         <v>34</v>
@@ -5979,7 +5992,7 @@
         <v>41</v>
       </c>
       <c r="T90" s="5" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="X90" s="4"/>
       <c r="Y90" s="4"/>
@@ -5992,7 +6005,7 @@
         <v>38</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C91" s="5" t="s">
         <v>34</v>
@@ -6025,7 +6038,7 @@
         <v>41</v>
       </c>
       <c r="T91" s="5" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="X91" s="4"/>
       <c r="Y91" s="4"/>
@@ -6038,7 +6051,7 @@
         <v>38</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C92" s="5" t="s">
         <v>34</v>
@@ -6071,7 +6084,7 @@
         <v>41</v>
       </c>
       <c r="T92" s="5" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="X92" s="4"/>
       <c r="Y92" s="4"/>
@@ -6084,7 +6097,7 @@
         <v>38</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C93" s="5" t="s">
         <v>34</v>
@@ -6117,7 +6130,7 @@
         <v>41</v>
       </c>
       <c r="T93" s="5" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="X93" s="4"/>
       <c r="Y93" s="4"/>
@@ -6130,7 +6143,7 @@
         <v>38</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C94" s="5" t="s">
         <v>16</v>
@@ -6163,7 +6176,7 @@
         <v>42</v>
       </c>
       <c r="T94" s="5" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="X94" s="4"/>
       <c r="Y94" s="4"/>
@@ -6176,7 +6189,7 @@
         <v>38</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C95" s="5" t="s">
         <v>16</v>
@@ -6209,7 +6222,7 @@
         <v>42</v>
       </c>
       <c r="T95" s="5" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="X95" s="4"/>
       <c r="Y95" s="4"/>
@@ -6222,7 +6235,7 @@
         <v>38</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C96" s="5" t="s">
         <v>16</v>
@@ -6255,7 +6268,7 @@
         <v>42</v>
       </c>
       <c r="T96" s="5" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="X96" s="4"/>
       <c r="Y96" s="4"/>
@@ -6268,7 +6281,7 @@
         <v>38</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C97" s="5" t="s">
         <v>16</v>
@@ -6301,7 +6314,7 @@
         <v>42</v>
       </c>
       <c r="T97" s="5" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="X97" s="4"/>
       <c r="Y97" s="4"/>
@@ -6314,7 +6327,7 @@
         <v>43</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C98" s="5" t="s">
         <v>16</v>
@@ -6358,7 +6371,7 @@
         <v>43</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C99" s="5" t="s">
         <v>16</v>
@@ -6402,7 +6415,7 @@
         <v>43</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C100" s="5" t="s">
         <v>16</v>
@@ -6446,7 +6459,7 @@
         <v>43</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C101" s="5" t="s">
         <v>16</v>
@@ -6490,7 +6503,7 @@
         <v>43</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C102" s="5" t="s">
         <v>16</v>
@@ -6502,7 +6515,7 @@
         <v>18</v>
       </c>
       <c r="F102" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="G102" s="5">
         <v>1</v>
@@ -6533,7 +6546,7 @@
         <v>43</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C103" s="5" t="s">
         <v>16</v>
@@ -6545,7 +6558,7 @@
         <v>18</v>
       </c>
       <c r="F103" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="G103" s="5">
         <v>2</v>
@@ -6576,7 +6589,7 @@
         <v>43</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C104" s="5" t="s">
         <v>16</v>
@@ -6588,7 +6601,7 @@
         <v>18</v>
       </c>
       <c r="F104" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="G104" s="5">
         <v>3</v>
@@ -6619,7 +6632,7 @@
         <v>43</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C105" s="5" t="s">
         <v>16</v>
@@ -6631,7 +6644,7 @@
         <v>18</v>
       </c>
       <c r="F105" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="G105" s="5">
         <v>4</v>
@@ -6662,7 +6675,7 @@
         <v>43</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C106" s="5" t="s">
         <v>16</v>
@@ -6705,7 +6718,7 @@
         <v>43</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C107" s="5" t="s">
         <v>16</v>
@@ -6748,7 +6761,7 @@
         <v>43</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C108" s="5" t="s">
         <v>16</v>
@@ -6791,7 +6804,7 @@
         <v>43</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C109" s="5" t="s">
         <v>16</v>
@@ -7006,7 +7019,7 @@
         <v>43</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>304</v>
+        <v>380</v>
       </c>
       <c r="C114" s="5" t="s">
         <v>16</v>
@@ -7036,7 +7049,7 @@
         <v>20</v>
       </c>
       <c r="R114" s="6" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="S114" s="6"/>
       <c r="X114" s="4"/>
@@ -7050,7 +7063,7 @@
         <v>43</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>304</v>
+        <v>380</v>
       </c>
       <c r="C115" s="5" t="s">
         <v>16</v>
@@ -7080,7 +7093,7 @@
         <v>20</v>
       </c>
       <c r="R115" s="6" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="S115" s="6"/>
       <c r="X115" s="4"/>
@@ -7094,7 +7107,7 @@
         <v>43</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>304</v>
+        <v>380</v>
       </c>
       <c r="C116" s="5" t="s">
         <v>16</v>
@@ -7124,7 +7137,7 @@
         <v>20</v>
       </c>
       <c r="R116" s="6" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="S116" s="6"/>
       <c r="X116" s="4"/>
@@ -7138,7 +7151,7 @@
         <v>43</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>304</v>
+        <v>380</v>
       </c>
       <c r="C117" s="5" t="s">
         <v>16</v>
@@ -7168,7 +7181,7 @@
         <v>20</v>
       </c>
       <c r="R117" s="6" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="S117" s="6"/>
       <c r="X117" s="4"/>
@@ -7182,7 +7195,7 @@
         <v>43</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>303</v>
+        <v>381</v>
       </c>
       <c r="C118" s="5" t="s">
         <v>16</v>
@@ -7212,7 +7225,7 @@
         <v>20</v>
       </c>
       <c r="R118" s="6" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="S118" s="6"/>
       <c r="X118" s="4"/>
@@ -7226,7 +7239,7 @@
         <v>43</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>303</v>
+        <v>381</v>
       </c>
       <c r="C119" s="5" t="s">
         <v>16</v>
@@ -7256,7 +7269,7 @@
         <v>20</v>
       </c>
       <c r="R119" s="6" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="S119" s="6"/>
       <c r="X119" s="4"/>
@@ -7270,7 +7283,7 @@
         <v>43</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>303</v>
+        <v>381</v>
       </c>
       <c r="C120" s="5" t="s">
         <v>16</v>
@@ -7300,7 +7313,7 @@
         <v>20</v>
       </c>
       <c r="R120" s="6" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="S120" s="6"/>
       <c r="X120" s="4"/>
@@ -7314,7 +7327,7 @@
         <v>43</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>303</v>
+        <v>381</v>
       </c>
       <c r="C121" s="5" t="s">
         <v>16</v>
@@ -7344,7 +7357,7 @@
         <v>20</v>
       </c>
       <c r="R121" s="6" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="S121" s="6"/>
       <c r="X121" s="4"/>
@@ -7358,7 +7371,7 @@
         <v>47</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C122" s="5" t="s">
         <v>16</v>
@@ -7397,12 +7410,12 @@
         <v>48</v>
       </c>
       <c r="T122" s="7" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="X122" s="4"/>
       <c r="Y122" s="4"/>
       <c r="Z122" s="5" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="AA122" s="5" t="s">
         <v>20</v>
@@ -7414,7 +7427,7 @@
         <v>47</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C123" s="5" t="s">
         <v>16</v>
@@ -7453,12 +7466,12 @@
         <v>48</v>
       </c>
       <c r="T123" s="7" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="X123" s="4"/>
       <c r="Y123" s="4"/>
       <c r="Z123" s="5" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="AA123" s="5" t="s">
         <v>20</v>
@@ -7470,7 +7483,7 @@
         <v>47</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C124" s="5" t="s">
         <v>16</v>
@@ -7509,12 +7522,12 @@
         <v>48</v>
       </c>
       <c r="T124" s="7" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="X124" s="4"/>
       <c r="Y124" s="4"/>
       <c r="Z124" s="5" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="AA124" s="5" t="s">
         <v>20</v>
@@ -7526,7 +7539,7 @@
         <v>47</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C125" s="5" t="s">
         <v>16</v>
@@ -7565,12 +7578,12 @@
         <v>48</v>
       </c>
       <c r="T125" s="7" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="X125" s="4"/>
       <c r="Y125" s="4"/>
       <c r="Z125" s="5" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="AA125" s="5" t="s">
         <v>20</v>
@@ -7582,7 +7595,7 @@
         <v>47</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C126" s="5" t="s">
         <v>16</v>
@@ -7617,7 +7630,7 @@
       <c r="X126" s="4"/>
       <c r="Y126" s="4"/>
       <c r="Z126" s="5" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="AA126" s="4"/>
       <c r="AB126" s="4"/>
@@ -7627,7 +7640,7 @@
         <v>47</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C127" s="5" t="s">
         <v>16</v>
@@ -7662,7 +7675,7 @@
       <c r="X127" s="4"/>
       <c r="Y127" s="4"/>
       <c r="Z127" s="5" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="AA127" s="4"/>
       <c r="AB127" s="4"/>
@@ -7672,7 +7685,7 @@
         <v>47</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C128" s="5" t="s">
         <v>16</v>
@@ -7707,7 +7720,7 @@
       <c r="X128" s="4"/>
       <c r="Y128" s="4"/>
       <c r="Z128" s="5" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="AA128" s="4"/>
       <c r="AB128" s="4"/>
@@ -7717,7 +7730,7 @@
         <v>47</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C129" s="5" t="s">
         <v>16</v>
@@ -7752,7 +7765,7 @@
       <c r="X129" s="4"/>
       <c r="Y129" s="4"/>
       <c r="Z129" s="5" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="AA129" s="4"/>
       <c r="AB129" s="4"/>
@@ -7762,7 +7775,7 @@
         <v>47</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C130" s="5" t="s">
         <v>16</v>
@@ -7795,7 +7808,7 @@
         <v>48</v>
       </c>
       <c r="T130" s="5" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="X130" s="4"/>
       <c r="Y130" s="4"/>
@@ -7808,7 +7821,7 @@
         <v>47</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C131" s="5" t="s">
         <v>16</v>
@@ -7841,7 +7854,7 @@
         <v>48</v>
       </c>
       <c r="T131" s="5" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="X131" s="4"/>
       <c r="Y131" s="4"/>
@@ -7854,7 +7867,7 @@
         <v>47</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C132" s="5" t="s">
         <v>16</v>
@@ -7887,7 +7900,7 @@
         <v>48</v>
       </c>
       <c r="T132" s="5" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="X132" s="4"/>
       <c r="Y132" s="4"/>
@@ -7900,7 +7913,7 @@
         <v>47</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C133" s="5" t="s">
         <v>16</v>
@@ -7933,7 +7946,7 @@
         <v>48</v>
       </c>
       <c r="T133" s="5" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="X133" s="4"/>
       <c r="Y133" s="4"/>
@@ -7946,7 +7959,7 @@
         <v>47</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C134" s="5" t="s">
         <v>16</v>
@@ -7979,7 +7992,7 @@
         <v>48</v>
       </c>
       <c r="T134" s="5" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="X134" s="4"/>
       <c r="Y134" s="4"/>
@@ -7992,7 +8005,7 @@
         <v>47</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C135" s="5" t="s">
         <v>16</v>
@@ -8025,7 +8038,7 @@
         <v>48</v>
       </c>
       <c r="T135" s="5" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="X135" s="4"/>
       <c r="Y135" s="4"/>
@@ -8038,7 +8051,7 @@
         <v>47</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C136" s="5" t="s">
         <v>16</v>
@@ -8071,7 +8084,7 @@
         <v>48</v>
       </c>
       <c r="T136" s="5" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="X136" s="4"/>
       <c r="Y136" s="4"/>
@@ -8084,7 +8097,7 @@
         <v>47</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C137" s="5" t="s">
         <v>16</v>
@@ -8117,7 +8130,7 @@
         <v>48</v>
       </c>
       <c r="T137" s="5" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="X137" s="4"/>
       <c r="Y137" s="4"/>
@@ -8130,7 +8143,7 @@
         <v>47</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C138" s="5" t="s">
         <v>16</v>
@@ -8139,10 +8152,10 @@
         <v>299</v>
       </c>
       <c r="E138" s="5" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="F138" s="5" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="G138" s="5">
         <v>1</v>
@@ -8163,7 +8176,7 @@
         <v>48</v>
       </c>
       <c r="T138" s="5" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="X138" s="4"/>
       <c r="Y138" s="4"/>
@@ -8176,7 +8189,7 @@
         <v>47</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C139" s="5" t="s">
         <v>16</v>
@@ -8185,10 +8198,10 @@
         <v>299</v>
       </c>
       <c r="E139" s="5" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="F139" s="5" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="G139" s="5">
         <v>2</v>
@@ -8209,7 +8222,7 @@
         <v>48</v>
       </c>
       <c r="T139" s="5" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="X139" s="4"/>
       <c r="Y139" s="4"/>
@@ -8222,7 +8235,7 @@
         <v>47</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C140" s="5" t="s">
         <v>16</v>
@@ -8231,10 +8244,10 @@
         <v>299</v>
       </c>
       <c r="E140" s="5" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="F140" s="5" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="G140" s="5">
         <v>3</v>
@@ -8255,7 +8268,7 @@
         <v>48</v>
       </c>
       <c r="T140" s="5" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="X140" s="4"/>
       <c r="Y140" s="4"/>
@@ -8268,7 +8281,7 @@
         <v>47</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C141" s="5" t="s">
         <v>16</v>
@@ -8277,10 +8290,10 @@
         <v>299</v>
       </c>
       <c r="E141" s="5" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="F141" s="5" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="G141" s="5">
         <v>4</v>
@@ -8301,7 +8314,7 @@
         <v>48</v>
       </c>
       <c r="T141" s="5" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="X141" s="4"/>
       <c r="Y141" s="4"/>
@@ -8314,7 +8327,7 @@
         <v>47</v>
       </c>
       <c r="B142" s="5" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C142" s="5" t="s">
         <v>16</v>
@@ -8347,7 +8360,7 @@
         <v>48</v>
       </c>
       <c r="T142" s="5" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="X142" s="4"/>
       <c r="Y142" s="4"/>
@@ -8360,7 +8373,7 @@
         <v>47</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C143" s="5" t="s">
         <v>16</v>
@@ -8393,7 +8406,7 @@
         <v>48</v>
       </c>
       <c r="T143" s="5" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="X143" s="4"/>
       <c r="Y143" s="4"/>
@@ -8406,7 +8419,7 @@
         <v>47</v>
       </c>
       <c r="B144" s="5" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C144" s="5" t="s">
         <v>16</v>
@@ -8439,7 +8452,7 @@
         <v>48</v>
       </c>
       <c r="T144" s="5" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="X144" s="4"/>
       <c r="Y144" s="4"/>
@@ -8452,7 +8465,7 @@
         <v>47</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C145" s="5" t="s">
         <v>16</v>
@@ -8485,7 +8498,7 @@
         <v>48</v>
       </c>
       <c r="T145" s="5" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="X145" s="4"/>
       <c r="Y145" s="4"/>
@@ -8498,7 +8511,7 @@
         <v>47</v>
       </c>
       <c r="B146" s="5" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C146" s="5" t="s">
         <v>16</v>
@@ -8531,7 +8544,7 @@
         <v>48</v>
       </c>
       <c r="T146" s="5" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="X146" s="4"/>
       <c r="Y146" s="4"/>
@@ -8544,7 +8557,7 @@
         <v>47</v>
       </c>
       <c r="B147" s="5" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C147" s="5" t="s">
         <v>16</v>
@@ -8577,7 +8590,7 @@
         <v>48</v>
       </c>
       <c r="T147" s="5" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="X147" s="4"/>
       <c r="Y147" s="4"/>
@@ -8590,7 +8603,7 @@
         <v>47</v>
       </c>
       <c r="B148" s="5" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C148" s="5" t="s">
         <v>16</v>
@@ -8623,7 +8636,7 @@
         <v>48</v>
       </c>
       <c r="T148" s="5" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="X148" s="4"/>
       <c r="Y148" s="4"/>
@@ -8636,7 +8649,7 @@
         <v>47</v>
       </c>
       <c r="B149" s="5" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C149" s="5" t="s">
         <v>16</v>
@@ -8669,7 +8682,7 @@
         <v>48</v>
       </c>
       <c r="T149" s="5" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="X149" s="4"/>
       <c r="Y149" s="4"/>
@@ -8715,7 +8728,7 @@
         <v>48</v>
       </c>
       <c r="T150" s="5" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="X150" s="4"/>
       <c r="Y150" s="4"/>
@@ -8761,7 +8774,7 @@
         <v>48</v>
       </c>
       <c r="T151" s="5" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="X151" s="4"/>
       <c r="Y151" s="4"/>
@@ -8807,7 +8820,7 @@
         <v>48</v>
       </c>
       <c r="T152" s="5" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="X152" s="4"/>
       <c r="Y152" s="4"/>
@@ -8853,7 +8866,7 @@
         <v>48</v>
       </c>
       <c r="T153" s="5" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="X153" s="4"/>
       <c r="Y153" s="4"/>
@@ -8866,7 +8879,7 @@
         <v>49</v>
       </c>
       <c r="B154" s="5" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C154" s="5" t="s">
         <v>16</v>
@@ -8875,10 +8888,10 @@
         <v>17</v>
       </c>
       <c r="E154" s="5" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="F154" s="5" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="G154" s="5">
         <v>1</v>
@@ -8909,7 +8922,7 @@
         <v>49</v>
       </c>
       <c r="B155" s="5" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C155" s="5" t="s">
         <v>16</v>
@@ -8918,10 +8931,10 @@
         <v>17</v>
       </c>
       <c r="E155" s="5" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="F155" s="5" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="G155" s="5">
         <v>2</v>
@@ -8952,7 +8965,7 @@
         <v>49</v>
       </c>
       <c r="B156" s="5" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C156" s="5" t="s">
         <v>16</v>
@@ -8961,10 +8974,10 @@
         <v>17</v>
       </c>
       <c r="E156" s="5" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="F156" s="5" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="G156" s="5">
         <v>3</v>
@@ -8995,7 +9008,7 @@
         <v>49</v>
       </c>
       <c r="B157" s="5" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C157" s="5" t="s">
         <v>16</v>
@@ -9004,10 +9017,10 @@
         <v>17</v>
       </c>
       <c r="E157" s="5" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="F157" s="5" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="G157" s="5">
         <v>4</v>
@@ -9038,7 +9051,7 @@
         <v>49</v>
       </c>
       <c r="B158" s="5" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C158" s="5" t="s">
         <v>16</v>
@@ -9081,7 +9094,7 @@
         <v>49</v>
       </c>
       <c r="B159" s="5" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C159" s="5" t="s">
         <v>16</v>
@@ -9124,7 +9137,7 @@
         <v>49</v>
       </c>
       <c r="B160" s="5" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C160" s="5" t="s">
         <v>16</v>
@@ -9167,7 +9180,7 @@
         <v>49</v>
       </c>
       <c r="B161" s="5" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C161" s="5" t="s">
         <v>16</v>
@@ -9210,7 +9223,7 @@
         <v>49</v>
       </c>
       <c r="B162" s="5" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C162" s="5" t="s">
         <v>16</v>
@@ -9253,7 +9266,7 @@
         <v>49</v>
       </c>
       <c r="B163" s="5" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C163" s="5" t="s">
         <v>16</v>
@@ -9296,7 +9309,7 @@
         <v>49</v>
       </c>
       <c r="B164" s="5" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C164" s="5" t="s">
         <v>16</v>
@@ -9339,7 +9352,7 @@
         <v>49</v>
       </c>
       <c r="B165" s="5" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C165" s="5" t="s">
         <v>16</v>
@@ -9382,7 +9395,7 @@
         <v>49</v>
       </c>
       <c r="B166" s="5" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C166" s="5" t="s">
         <v>16</v>
@@ -9391,10 +9404,10 @@
         <v>301</v>
       </c>
       <c r="E166" s="5" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="F166" s="5" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="G166" s="5">
         <v>1</v>
@@ -9412,7 +9425,7 @@
         <v>20</v>
       </c>
       <c r="R166" s="5" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="X166" s="4"/>
       <c r="Y166" s="4"/>
@@ -9425,7 +9438,7 @@
         <v>49</v>
       </c>
       <c r="B167" s="5" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C167" s="5" t="s">
         <v>16</v>
@@ -9434,10 +9447,10 @@
         <v>301</v>
       </c>
       <c r="E167" s="5" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="F167" s="5" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="G167" s="5">
         <v>2</v>
@@ -9455,7 +9468,7 @@
         <v>20</v>
       </c>
       <c r="R167" s="5" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="X167" s="4"/>
       <c r="Y167" s="4"/>
@@ -9468,7 +9481,7 @@
         <v>49</v>
       </c>
       <c r="B168" s="5" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C168" s="5" t="s">
         <v>16</v>
@@ -9477,10 +9490,10 @@
         <v>301</v>
       </c>
       <c r="E168" s="5" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="F168" s="5" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="G168" s="5">
         <v>3</v>
@@ -9498,7 +9511,7 @@
         <v>20</v>
       </c>
       <c r="R168" s="5" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="X168" s="4"/>
       <c r="Y168" s="4"/>
@@ -9511,7 +9524,7 @@
         <v>49</v>
       </c>
       <c r="B169" s="5" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C169" s="5" t="s">
         <v>16</v>
@@ -9520,10 +9533,10 @@
         <v>301</v>
       </c>
       <c r="E169" s="5" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="F169" s="5" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="G169" s="5">
         <v>4</v>
@@ -9541,7 +9554,7 @@
         <v>20</v>
       </c>
       <c r="R169" s="5" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="X169" s="4"/>
       <c r="Y169" s="4"/>
@@ -9554,7 +9567,7 @@
         <v>49</v>
       </c>
       <c r="B170" s="5" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C170" s="5" t="s">
         <v>16</v>
@@ -9584,7 +9597,7 @@
         <v>20</v>
       </c>
       <c r="R170" s="5" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="X170" s="4"/>
       <c r="Y170" s="4"/>
@@ -9597,7 +9610,7 @@
         <v>49</v>
       </c>
       <c r="B171" s="5" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C171" s="5" t="s">
         <v>16</v>
@@ -9627,7 +9640,7 @@
         <v>20</v>
       </c>
       <c r="R171" s="5" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="X171" s="4"/>
       <c r="Y171" s="4"/>
@@ -9640,7 +9653,7 @@
         <v>49</v>
       </c>
       <c r="B172" s="5" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C172" s="5" t="s">
         <v>16</v>
@@ -9670,7 +9683,7 @@
         <v>20</v>
       </c>
       <c r="R172" s="5" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="X172" s="4"/>
       <c r="Y172" s="4"/>
@@ -9683,7 +9696,7 @@
         <v>49</v>
       </c>
       <c r="B173" s="5" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C173" s="5" t="s">
         <v>16</v>
@@ -9713,7 +9726,7 @@
         <v>20</v>
       </c>
       <c r="R173" s="5" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="X173" s="4"/>
       <c r="Y173" s="4"/>
@@ -9726,7 +9739,7 @@
         <v>49</v>
       </c>
       <c r="B174" s="5" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C174" s="5" t="s">
         <v>16</v>
@@ -9756,7 +9769,7 @@
         <v>20</v>
       </c>
       <c r="R174" s="5" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="X174" s="4"/>
       <c r="Y174" s="4"/>
@@ -9769,7 +9782,7 @@
         <v>49</v>
       </c>
       <c r="B175" s="5" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C175" s="5" t="s">
         <v>16</v>
@@ -9799,7 +9812,7 @@
         <v>20</v>
       </c>
       <c r="R175" s="5" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="X175" s="4"/>
       <c r="Y175" s="4"/>
@@ -9812,7 +9825,7 @@
         <v>49</v>
       </c>
       <c r="B176" s="5" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C176" s="5" t="s">
         <v>16</v>
@@ -9842,7 +9855,7 @@
         <v>20</v>
       </c>
       <c r="R176" s="5" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="X176" s="4"/>
       <c r="Y176" s="4"/>
@@ -9855,7 +9868,7 @@
         <v>49</v>
       </c>
       <c r="B177" s="5" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C177" s="5" t="s">
         <v>16</v>
@@ -9885,7 +9898,7 @@
         <v>20</v>
       </c>
       <c r="R177" s="5" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="X177" s="4"/>
       <c r="Y177" s="4"/>
@@ -9898,7 +9911,7 @@
         <v>51</v>
       </c>
       <c r="B178" s="5" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C178" s="5" t="s">
         <v>16</v>
@@ -9941,7 +9954,7 @@
         <v>51</v>
       </c>
       <c r="B179" s="5" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C179" s="5" t="s">
         <v>16</v>
@@ -9984,7 +9997,7 @@
         <v>51</v>
       </c>
       <c r="B180" s="5" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C180" s="5" t="s">
         <v>16</v>
@@ -10027,7 +10040,7 @@
         <v>51</v>
       </c>
       <c r="B181" s="5" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C181" s="5" t="s">
         <v>16</v>
@@ -10242,7 +10255,7 @@
         <v>55</v>
       </c>
       <c r="B186" s="5" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C186" s="5" t="s">
         <v>16</v>
@@ -10263,7 +10276,7 @@
         <v>0.16589999999999999</v>
       </c>
       <c r="I186" s="5">
-        <v>0.144813</v>
+        <v>0.15324199999999999</v>
       </c>
       <c r="J186" s="5" t="s">
         <v>20</v>
@@ -10285,7 +10298,7 @@
         <v>55</v>
       </c>
       <c r="B187" s="5" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C187" s="5" t="s">
         <v>16</v>
@@ -10306,7 +10319,7 @@
         <v>0.20150000000000001</v>
       </c>
       <c r="I187" s="5">
-        <v>0.144706</v>
+        <v>0.15313499999999999</v>
       </c>
       <c r="J187" s="5" t="s">
         <v>20</v>
@@ -10328,7 +10341,7 @@
         <v>55</v>
       </c>
       <c r="B188" s="5" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C188" s="5" t="s">
         <v>16</v>
@@ -10349,7 +10362,7 @@
         <v>0.23599999999999999</v>
       </c>
       <c r="I188" s="5">
-        <v>0.14469099999999999</v>
+        <v>0.15312000000000001</v>
       </c>
       <c r="J188" s="5" t="s">
         <v>20</v>
@@ -10371,7 +10384,7 @@
         <v>55</v>
       </c>
       <c r="B189" s="5" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C189" s="5" t="s">
         <v>16</v>
@@ -10392,7 +10405,7 @@
         <v>0.29570000000000002</v>
       </c>
       <c r="I189" s="5">
-        <v>0.14457999999999999</v>
+        <v>0.15300900000000001</v>
       </c>
       <c r="J189" s="5" t="s">
         <v>20</v>
@@ -10414,7 +10427,7 @@
         <v>55</v>
       </c>
       <c r="B190" s="5" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C190" s="5" t="s">
         <v>16</v>
@@ -10435,7 +10448,7 @@
         <v>7.5899999999999995E-2</v>
       </c>
       <c r="I190" s="5">
-        <v>0.103813</v>
+        <v>0.11224199999999999</v>
       </c>
       <c r="J190" s="5" t="s">
         <v>20</v>
@@ -10457,7 +10470,7 @@
         <v>55</v>
       </c>
       <c r="B191" s="5" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C191" s="5" t="s">
         <v>16</v>
@@ -10478,7 +10491,7 @@
         <v>0.1115</v>
       </c>
       <c r="I191" s="5">
-        <v>9.8605999999999999E-2</v>
+        <v>0.10703500000000001</v>
       </c>
       <c r="J191" s="5" t="s">
         <v>20</v>
@@ -10500,7 +10513,7 @@
         <v>55</v>
       </c>
       <c r="B192" s="5" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C192" s="5" t="s">
         <v>16</v>
@@ -10521,7 +10534,7 @@
         <v>0.11600000000000001</v>
       </c>
       <c r="I192" s="5">
-        <v>9.4590999999999995E-2</v>
+        <v>0.10302</v>
       </c>
       <c r="J192" s="5" t="s">
         <v>20</v>
@@ -10543,7 +10556,7 @@
         <v>55</v>
       </c>
       <c r="B193" s="5" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C193" s="5" t="s">
         <v>16</v>
@@ -10564,7 +10577,7 @@
         <v>0.1457</v>
       </c>
       <c r="I193" s="5">
-        <v>8.9698E-2</v>
+        <v>9.8127000000000006E-2</v>
       </c>
       <c r="J193" s="5" t="s">
         <v>20</v>
@@ -10586,7 +10599,7 @@
         <v>55</v>
       </c>
       <c r="B194" s="5" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C194" s="5" t="s">
         <v>16</v>
@@ -10607,7 +10620,7 @@
         <v>1.5900000000000001E-2</v>
       </c>
       <c r="I194" s="5">
-        <v>0.213813</v>
+        <v>0.222242</v>
       </c>
       <c r="J194" s="5" t="s">
         <v>20</v>
@@ -10629,7 +10642,7 @@
         <v>55</v>
       </c>
       <c r="B195" s="5" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C195" s="5" t="s">
         <v>16</v>
@@ -10650,7 +10663,7 @@
         <v>5.1499999999999997E-2</v>
       </c>
       <c r="I195" s="5">
-        <v>0.20860600000000001</v>
+        <v>0.21703500000000001</v>
       </c>
       <c r="J195" s="5" t="s">
         <v>20</v>
@@ -10672,7 +10685,7 @@
         <v>55</v>
       </c>
       <c r="B196" s="5" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C196" s="5" t="s">
         <v>16</v>
@@ -10693,7 +10706,7 @@
         <v>8.5999999999999993E-2</v>
       </c>
       <c r="I196" s="5">
-        <v>0.205591</v>
+        <v>0.21401999999999999</v>
       </c>
       <c r="J196" s="5" t="s">
         <v>20</v>
@@ -10715,7 +10728,7 @@
         <v>55</v>
       </c>
       <c r="B197" s="5" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C197" s="5" t="s">
         <v>16</v>
@@ -10736,7 +10749,7 @@
         <v>0.1457</v>
       </c>
       <c r="I197" s="5">
-        <v>0.20427999999999999</v>
+        <v>0.21270900000000001</v>
       </c>
       <c r="J197" s="5" t="s">
         <v>20</v>
@@ -10754,11 +10767,692 @@
       <c r="AB197" s="4"/>
     </row>
     <row r="198" spans="1:28" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A198" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="B198" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="C198" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D198" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E198" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F198" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G198" s="5">
+        <v>1</v>
+      </c>
+      <c r="H198" s="5">
+        <v>0.17519999999999999</v>
+      </c>
+      <c r="I198" s="5">
+        <v>9.7750000000000004E-2</v>
+      </c>
+      <c r="J198" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K198" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="R198" s="5" t="s">
+        <v>376</v>
+      </c>
       <c r="X198" s="4"/>
       <c r="Y198" s="4"/>
       <c r="Z198" s="4"/>
       <c r="AA198" s="4"/>
       <c r="AB198" s="4"/>
+    </row>
+    <row r="199" spans="1:28" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A199" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="B199" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="C199" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D199" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E199" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F199" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G199" s="5">
+        <v>2</v>
+      </c>
+      <c r="H199" s="5">
+        <v>0.23499999999999999</v>
+      </c>
+      <c r="I199" s="5">
+        <v>9.7750000000000004E-2</v>
+      </c>
+      <c r="J199" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K199" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="R199" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="X199" s="4"/>
+      <c r="Y199" s="4"/>
+      <c r="Z199" s="4"/>
+      <c r="AA199" s="4"/>
+      <c r="AB199" s="4"/>
+    </row>
+    <row r="200" spans="1:28" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A200" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="B200" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="C200" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D200" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E200" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F200" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G200" s="5">
+        <v>3</v>
+      </c>
+      <c r="H200" s="5">
+        <v>0.35499999999999998</v>
+      </c>
+      <c r="I200" s="5">
+        <v>9.35E-2</v>
+      </c>
+      <c r="J200" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K200" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="R200" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="X200" s="4"/>
+      <c r="Y200" s="4"/>
+      <c r="Z200" s="4"/>
+      <c r="AA200" s="4"/>
+      <c r="AB200" s="4"/>
+    </row>
+    <row r="201" spans="1:28" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A201" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="B201" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="C201" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D201" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E201" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F201" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G201" s="5">
+        <v>4</v>
+      </c>
+      <c r="H201" s="5">
+        <v>0.65</v>
+      </c>
+      <c r="I201" s="5">
+        <v>9.35E-2</v>
+      </c>
+      <c r="J201" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K201" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="R201" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="X201" s="4"/>
+      <c r="Y201" s="4"/>
+      <c r="Z201" s="4"/>
+      <c r="AA201" s="4"/>
+      <c r="AB201" s="4"/>
+    </row>
+    <row r="202" spans="1:28" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A202" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="B202" s="5" t="s">
+        <v>377</v>
+      </c>
+      <c r="C202" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D202" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E202" s="5" t="s">
+        <v>348</v>
+      </c>
+      <c r="F202" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G202" s="5">
+        <v>1</v>
+      </c>
+      <c r="H202" s="5">
+        <v>0.17519999999999999</v>
+      </c>
+      <c r="I202" s="5">
+        <v>0.10005</v>
+      </c>
+      <c r="J202" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K202" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="R202" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="X202" s="4"/>
+      <c r="Y202" s="4"/>
+      <c r="Z202" s="4"/>
+      <c r="AA202" s="4"/>
+      <c r="AB202" s="4"/>
+    </row>
+    <row r="203" spans="1:28" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A203" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="B203" s="5" t="s">
+        <v>377</v>
+      </c>
+      <c r="C203" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D203" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E203" s="5" t="s">
+        <v>348</v>
+      </c>
+      <c r="F203" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G203" s="5">
+        <v>2</v>
+      </c>
+      <c r="H203" s="5">
+        <v>0.23499999999999999</v>
+      </c>
+      <c r="I203" s="5">
+        <v>0.10005</v>
+      </c>
+      <c r="J203" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K203" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="R203" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="X203" s="4"/>
+      <c r="Y203" s="4"/>
+      <c r="Z203" s="4"/>
+      <c r="AA203" s="4"/>
+      <c r="AB203" s="4"/>
+    </row>
+    <row r="204" spans="1:28" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A204" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="B204" s="5" t="s">
+        <v>377</v>
+      </c>
+      <c r="C204" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D204" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E204" s="5" t="s">
+        <v>348</v>
+      </c>
+      <c r="F204" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G204" s="5">
+        <v>3</v>
+      </c>
+      <c r="H204" s="5">
+        <v>0.35499999999999998</v>
+      </c>
+      <c r="I204" s="5">
+        <v>9.5699999999999993E-2</v>
+      </c>
+      <c r="J204" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K204" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="R204" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="X204" s="4"/>
+      <c r="Y204" s="4"/>
+      <c r="Z204" s="4"/>
+      <c r="AA204" s="4"/>
+      <c r="AB204" s="4"/>
+    </row>
+    <row r="205" spans="1:28" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A205" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="B205" s="5" t="s">
+        <v>377</v>
+      </c>
+      <c r="C205" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D205" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E205" s="5" t="s">
+        <v>348</v>
+      </c>
+      <c r="F205" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G205" s="5">
+        <v>4</v>
+      </c>
+      <c r="H205" s="5">
+        <v>0.65</v>
+      </c>
+      <c r="I205" s="5">
+        <v>9.5699999999999993E-2</v>
+      </c>
+      <c r="J205" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K205" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="R205" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="X205" s="4"/>
+      <c r="Y205" s="4"/>
+      <c r="Z205" s="4"/>
+      <c r="AA205" s="4"/>
+      <c r="AB205" s="4"/>
+    </row>
+    <row r="206" spans="1:28" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A206" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="B206" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="C206" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D206" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E206" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F206" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="G206" s="5">
+        <v>1</v>
+      </c>
+      <c r="H206" s="5">
+        <v>0.17519999999999999</v>
+      </c>
+      <c r="I206" s="5">
+        <v>0.10695</v>
+      </c>
+      <c r="J206" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K206" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="R206" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="X206" s="4"/>
+      <c r="Y206" s="4"/>
+      <c r="Z206" s="4"/>
+      <c r="AA206" s="4"/>
+      <c r="AB206" s="4"/>
+    </row>
+    <row r="207" spans="1:28" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A207" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="B207" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="C207" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D207" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E207" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F207" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="G207" s="5">
+        <v>2</v>
+      </c>
+      <c r="H207" s="5">
+        <v>0.23499999999999999</v>
+      </c>
+      <c r="I207" s="5">
+        <v>0.10695</v>
+      </c>
+      <c r="J207" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K207" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="R207" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="X207" s="4"/>
+      <c r="Y207" s="4"/>
+      <c r="Z207" s="4"/>
+      <c r="AA207" s="4"/>
+      <c r="AB207" s="4"/>
+    </row>
+    <row r="208" spans="1:28" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A208" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="B208" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="C208" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D208" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E208" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F208" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="G208" s="5">
+        <v>3</v>
+      </c>
+      <c r="H208" s="5">
+        <v>0.35499999999999998</v>
+      </c>
+      <c r="I208" s="5">
+        <v>0.1023</v>
+      </c>
+      <c r="J208" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K208" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="R208" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="X208" s="4"/>
+      <c r="Y208" s="4"/>
+      <c r="Z208" s="4"/>
+      <c r="AA208" s="4"/>
+      <c r="AB208" s="4"/>
+    </row>
+    <row r="209" spans="1:28" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A209" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="B209" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="C209" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D209" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E209" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F209" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="G209" s="5">
+        <v>4</v>
+      </c>
+      <c r="H209" s="5">
+        <v>0.65</v>
+      </c>
+      <c r="I209" s="5">
+        <v>0.1023</v>
+      </c>
+      <c r="J209" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K209" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="R209" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="X209" s="4"/>
+      <c r="Y209" s="4"/>
+      <c r="Z209" s="4"/>
+      <c r="AA209" s="4"/>
+      <c r="AB209" s="4"/>
+    </row>
+    <row r="210" spans="1:28" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A210" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="B210" s="5" t="s">
+        <v>379</v>
+      </c>
+      <c r="C210" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D210" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E210" s="5" t="s">
+        <v>348</v>
+      </c>
+      <c r="F210" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="G210" s="5">
+        <v>1</v>
+      </c>
+      <c r="H210" s="5">
+        <v>0.17519999999999999</v>
+      </c>
+      <c r="I210" s="5">
+        <v>0.10925</v>
+      </c>
+      <c r="J210" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K210" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="R210" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="X210" s="4"/>
+      <c r="Y210" s="4"/>
+      <c r="Z210" s="4"/>
+      <c r="AA210" s="4"/>
+      <c r="AB210" s="4"/>
+    </row>
+    <row r="211" spans="1:28" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A211" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="B211" s="5" t="s">
+        <v>379</v>
+      </c>
+      <c r="C211" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D211" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E211" s="5" t="s">
+        <v>348</v>
+      </c>
+      <c r="F211" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="G211" s="5">
+        <v>2</v>
+      </c>
+      <c r="H211" s="5">
+        <v>0.23499999999999999</v>
+      </c>
+      <c r="I211" s="5">
+        <v>0.10925</v>
+      </c>
+      <c r="J211" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K211" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="R211" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="X211" s="4"/>
+      <c r="Y211" s="4"/>
+      <c r="Z211" s="4"/>
+      <c r="AA211" s="4"/>
+      <c r="AB211" s="4"/>
+    </row>
+    <row r="212" spans="1:28" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A212" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="B212" s="5" t="s">
+        <v>379</v>
+      </c>
+      <c r="C212" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D212" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E212" s="5" t="s">
+        <v>348</v>
+      </c>
+      <c r="F212" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="G212" s="5">
+        <v>3</v>
+      </c>
+      <c r="H212" s="5">
+        <v>0.35499999999999998</v>
+      </c>
+      <c r="I212" s="5">
+        <v>0.1045</v>
+      </c>
+      <c r="J212" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K212" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="R212" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="X212" s="4"/>
+      <c r="Y212" s="4"/>
+      <c r="Z212" s="4"/>
+      <c r="AA212" s="4"/>
+      <c r="AB212" s="4"/>
+    </row>
+    <row r="213" spans="1:28" s="5" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A213" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="B213" s="5" t="s">
+        <v>379</v>
+      </c>
+      <c r="C213" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D213" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E213" s="5" t="s">
+        <v>348</v>
+      </c>
+      <c r="F213" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="G213" s="5">
+        <v>4</v>
+      </c>
+      <c r="H213" s="5">
+        <v>0.65</v>
+      </c>
+      <c r="I213" s="5">
+        <v>0.1045</v>
+      </c>
+      <c r="J213" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="K213" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="R213" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="X213" s="4"/>
+      <c r="Y213" s="4"/>
+      <c r="Z213" s="4"/>
+      <c r="AA213" s="4"/>
+      <c r="AB213" s="4"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AG1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
